--- a/Design Files/DC-Motor-Driver/Deliverables/BOM/eSpark BOM.xlsx
+++ b/Design Files/DC-Motor-Driver/Deliverables/BOM/eSpark BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\manarharake-motordriver\Design Files\DC-Motor-Driver\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\manarharake-motordriver\Design Files\DC-Motor-Driver\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="386">
   <si>
     <t>Component list</t>
   </si>
@@ -397,24 +397,9 @@
     <t>Diode</t>
   </si>
   <si>
-    <t>D1, D6</t>
-  </si>
-  <si>
-    <t>DIODE SCHOTTKY 30V 100MA SOT323</t>
-  </si>
-  <si>
-    <t>SOT_323</t>
-  </si>
-  <si>
-    <t>BAT54CWT1G</t>
-  </si>
-  <si>
     <t>ON Semiconductor / Fairchild</t>
   </si>
   <si>
-    <t>C77321</t>
-  </si>
-  <si>
     <t>D2, D5</t>
   </si>
   <si>
@@ -1123,15 +1108,6 @@
     <t>Force Sensor</t>
   </si>
   <si>
-    <t>LithiumIonBatteries ROHS</t>
-  </si>
-  <si>
-    <t>maxell CR2032</t>
-  </si>
-  <si>
-    <t>C62366</t>
-  </si>
-  <si>
     <t>Motor</t>
   </si>
   <si>
@@ -1142,6 +1118,66 @@
   </si>
   <si>
     <t>PJRC</t>
+  </si>
+  <si>
+    <t>D1, D7</t>
+  </si>
+  <si>
+    <t>60V 700mV@1A 1A SMA(DO-214AC) Schottky Barrier Diodes (SBD) ROHS</t>
+  </si>
+  <si>
+    <t>SS16</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>C2481</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>Single 3.01V~3.22V 500mW 3.1V SOD-123 Zener Diodes ROHS</t>
+  </si>
+  <si>
+    <t>SOD-123</t>
+  </si>
+  <si>
+    <t>LBZT52B3V0T1G</t>
+  </si>
+  <si>
+    <t>LRC</t>
+  </si>
+  <si>
+    <t>C2972805</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>RES SMD 100 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-07100RL</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>0603WAF1000T5E</t>
+  </si>
+  <si>
+    <t>C22775</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ML2032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3V Li-ion Rechargeable Battery </t>
+  </si>
+  <si>
+    <t>Aliexpress</t>
   </si>
 </sst>
 </file>
@@ -1153,7 +1189,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1334,6 +1370,19 @@
       <sz val="14"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1602,7 +1651,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1858,6 +1907,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2243,7 +2301,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:V73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="63" customWidth="1"/>
@@ -2268,7 +2326,7 @@
     <col min="22" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:22">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2289,7 +2347,7 @@
       <c r="R1" s="83"/>
       <c r="S1" s="84"/>
     </row>
-    <row r="2" spans="1:19" ht="31.5">
+    <row r="2" spans="1:22" ht="31.5">
       <c r="A2" s="2"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2314,7 +2372,7 @@
       <c r="R2" s="9"/>
       <c r="S2" s="48"/>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:22">
       <c r="A3" s="2"/>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
@@ -2339,7 +2397,7 @@
       <c r="R3" s="13"/>
       <c r="S3" s="87"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:22">
       <c r="A4" s="2"/>
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
@@ -2364,7 +2422,7 @@
       <c r="R4" s="17"/>
       <c r="S4" s="88"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:22">
       <c r="A5" s="2"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
@@ -2389,7 +2447,7 @@
       <c r="R5" s="17"/>
       <c r="S5" s="88"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:22">
       <c r="A6" s="2"/>
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
@@ -2410,7 +2468,7 @@
       <c r="R6" s="17"/>
       <c r="S6" s="88"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:22">
       <c r="A7" s="2"/>
       <c r="B7" s="22"/>
       <c r="C7" s="23"/>
@@ -2431,7 +2489,7 @@
       <c r="R7" s="26"/>
       <c r="S7" s="88"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1">
+    <row r="8" spans="1:22" ht="15.75" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="27"/>
       <c r="C8" s="28"/>
@@ -2452,7 +2510,7 @@
       <c r="R8" s="26"/>
       <c r="S8" s="88"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1">
+    <row r="9" spans="1:22" ht="15.75" thickBot="1">
       <c r="A9" s="2"/>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -2509,10 +2567,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:22">
       <c r="A10" s="2"/>
       <c r="B10" s="33">
-        <f t="shared" ref="B10:B69" si="0">ROW(B10)-ROW($B$9)</f>
+        <f t="shared" ref="B10:B71" si="0">ROW(B10)-ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="34" t="s">
@@ -2546,7 +2604,7 @@
         <v>4</v>
       </c>
       <c r="M10" s="35">
-        <f t="shared" ref="M10:M69" si="1">L10*5</f>
+        <f t="shared" ref="M10:M71" si="1">L10*5</f>
         <v>20</v>
       </c>
       <c r="N10" s="35">
@@ -2559,14 +2617,14 @@
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="Q10" s="42">
-        <f t="shared" ref="Q10:Q68" si="2">P10*N10</f>
+        <f t="shared" ref="Q10:Q70" si="2">P10*N10</f>
         <v>0.41000000000000003</v>
       </c>
       <c r="R10" s="35"/>
       <c r="S10" s="64"/>
     </row>
-    <row r="11" spans="1:19" ht="36">
-      <c r="A11" s="2"/>
+    <row r="11" spans="1:22" s="1" customFormat="1" ht="36">
+      <c r="A11" s="32"/>
       <c r="B11" s="36">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2620,8 +2678,10 @@
       </c>
       <c r="R11" s="37"/>
       <c r="S11" s="37"/>
-    </row>
-    <row r="12" spans="1:19" ht="24">
+      <c r="U11"/>
+      <c r="V11"/>
+    </row>
+    <row r="12" spans="1:22" ht="24">
       <c r="A12" s="2"/>
       <c r="B12" s="33">
         <f t="shared" si="0"/>
@@ -2677,7 +2737,7 @@
       <c r="R12" s="35"/>
       <c r="S12" s="64"/>
     </row>
-    <row r="13" spans="1:19" ht="24">
+    <row r="13" spans="1:22" ht="24">
       <c r="A13" s="2"/>
       <c r="B13" s="36">
         <f t="shared" si="0"/>
@@ -2733,7 +2793,7 @@
       <c r="R13" s="37"/>
       <c r="S13" s="37"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:22">
       <c r="A14" s="2"/>
       <c r="B14" s="33">
         <f t="shared" si="0"/>
@@ -2789,7 +2849,7 @@
       <c r="R14" s="35"/>
       <c r="S14" s="64"/>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:22">
       <c r="A15" s="2"/>
       <c r="B15" s="36">
         <f t="shared" si="0"/>
@@ -2845,7 +2905,7 @@
       <c r="R15" s="37"/>
       <c r="S15" s="37"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:22">
       <c r="A16" s="2"/>
       <c r="B16" s="33">
         <f t="shared" si="0"/>
@@ -3470,26 +3530,26 @@
       <c r="C27" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="37" t="s">
+      <c r="D27" s="93" t="s">
+        <v>366</v>
+      </c>
+      <c r="E27" s="93" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="H27" s="37" t="s">
-        <v>129</v>
+      <c r="G27" s="93" t="s">
+        <v>368</v>
+      </c>
+      <c r="H27" s="93" t="s">
+        <v>369</v>
       </c>
       <c r="I27" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="37" t="s">
-        <v>130</v>
+      <c r="J27" s="93" t="s">
+        <v>370</v>
       </c>
       <c r="K27" s="37" t="s">
         <v>31</v>
@@ -3502,17 +3562,17 @@
         <v>10</v>
       </c>
       <c r="N27" s="37">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O27" s="43" t="s">
         <v>34</v>
       </c>
       <c r="P27" s="44">
-        <v>2.9100000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q27" s="44">
         <f t="shared" si="2"/>
-        <v>0.58200000000000007</v>
+        <v>0.75</v>
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="37"/>
@@ -3527,25 +3587,25 @@
         <v>124</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I28" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K28" s="35" t="s">
         <v>31</v>
@@ -3583,25 +3643,25 @@
         <v>124</v>
       </c>
       <c r="D29" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="37" t="s">
         <v>136</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>141</v>
       </c>
       <c r="K29" s="35" t="s">
         <v>31</v>
@@ -3639,25 +3699,25 @@
         <v>124</v>
       </c>
       <c r="D30" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="35" t="s">
         <v>142</v>
-      </c>
-      <c r="E30" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="G30" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="H30" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="35" t="s">
-        <v>147</v>
       </c>
       <c r="K30" s="35" t="s">
         <v>31</v>
@@ -3687,1596 +3747,1596 @@
     </row>
     <row r="31" spans="1:19" ht="24">
       <c r="A31" s="2"/>
-      <c r="B31" s="36">
+      <c r="B31" s="33">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="K31" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="37">
+      <c r="C31" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>371</v>
+      </c>
+      <c r="E31" s="93" t="s">
+        <v>372</v>
+      </c>
+      <c r="F31" s="93" t="s">
+        <v>373</v>
+      </c>
+      <c r="G31" s="93" t="s">
+        <v>374</v>
+      </c>
+      <c r="H31" s="93" t="s">
+        <v>375</v>
+      </c>
+      <c r="I31" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="93" t="s">
+        <v>376</v>
+      </c>
+      <c r="K31" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="93">
         <v>1</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="35">
+        <v>20</v>
+      </c>
+      <c r="O31" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P31" s="42">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="Q31" s="42">
+        <f t="shared" si="2"/>
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="R31" s="35"/>
+      <c r="S31" s="64"/>
+    </row>
+    <row r="32" spans="1:19" ht="24">
+      <c r="A32" s="2"/>
+      <c r="B32" s="36">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="K32" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="37">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="N32" s="37">
         <v>10</v>
       </c>
-      <c r="O31" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P31" s="44">
+      <c r="O32" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P32" s="44">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="Q31" s="44">
+      <c r="Q32" s="44">
         <f t="shared" si="2"/>
         <v>0.443</v>
       </c>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
-    </row>
-    <row r="32" spans="1:19">
-      <c r="A32" s="2"/>
-      <c r="B32" s="33">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="34" t="s">
+      <c r="R32" s="37"/>
+      <c r="S32" s="37"/>
+    </row>
+    <row r="33" spans="1:19">
+      <c r="A33" s="2"/>
+      <c r="B33" s="33">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D32" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="G32" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="K32" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" s="35">
+      <c r="K33" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="35">
         <v>2</v>
       </c>
-      <c r="M32" s="35">
+      <c r="M33" s="35">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N32" s="35">
+      <c r="N33" s="35">
         <v>100</v>
       </c>
-      <c r="O32" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P32" s="42">
+      <c r="O33" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="42">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="Q32" s="42">
+      <c r="Q33" s="42">
         <f t="shared" si="2"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="R32" s="35"/>
-      <c r="S32" s="64"/>
-    </row>
-    <row r="33" spans="1:19" ht="25.5">
-      <c r="A33" s="2"/>
-      <c r="B33" s="36">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="L33" s="39">
+      <c r="R33" s="35"/>
+      <c r="S33" s="64"/>
+    </row>
+    <row r="34" spans="1:19" ht="25.5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="36">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="L34" s="39">
         <v>6</v>
       </c>
-      <c r="M33" s="39">
+      <c r="M34" s="39">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q33" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R33" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="S33" s="37"/>
-    </row>
-    <row r="34" spans="1:19" ht="25.5">
-      <c r="A34" s="2"/>
-      <c r="B34" s="33">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="G34" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K34" s="40" t="s">
+      <c r="N34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q34" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="S34" s="37"/>
+    </row>
+    <row r="35" spans="1:19" ht="25.5">
+      <c r="A35" s="2"/>
+      <c r="B35" s="33">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="L34" s="40">
+      <c r="G35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="L35" s="40">
         <v>1</v>
       </c>
-      <c r="M34" s="40">
+      <c r="M35" s="40">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N34" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="O34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P34" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q34" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R34" s="50" t="s">
+      <c r="N35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q35" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="S35" s="64"/>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="2"/>
+      <c r="B36" s="36">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="S34" s="64"/>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="A35" s="2"/>
-      <c r="B35" s="36">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="38" t="s">
+      <c r="D36" s="37" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="H36" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="D35" s="37" t="s">
+      <c r="I36" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="37" t="s">
         <v>171</v>
       </c>
-      <c r="E35" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="F35" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="37" t="s">
-        <v>174</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="K35" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" s="37">
+      <c r="K36" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="37">
         <v>1</v>
       </c>
-      <c r="M35" s="37">
+      <c r="M36" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N36" s="37">
         <v>10</v>
       </c>
-      <c r="O35" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P35" s="44">
+      <c r="O36" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" s="44">
         <v>0.2029</v>
       </c>
-      <c r="Q35" s="44">
+      <c r="Q36" s="44">
         <f t="shared" si="2"/>
         <v>2.0289999999999999</v>
       </c>
-      <c r="R35" s="37"/>
-      <c r="S35" s="37"/>
-    </row>
-    <row r="36" spans="1:19" ht="24">
-      <c r="A36" s="2"/>
-      <c r="B36" s="33">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="34" t="s">
+      <c r="R36" s="37"/>
+      <c r="S36" s="37"/>
+    </row>
+    <row r="37" spans="1:19" ht="24">
+      <c r="A37" s="2"/>
+      <c r="B37" s="33">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G36" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="H36" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" s="35">
+      <c r="K37" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="35">
         <v>1</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M37" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N37" s="35">
         <v>10</v>
       </c>
-      <c r="O36" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P36" s="42">
+      <c r="O37" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="42">
         <v>0.13009999999999999</v>
       </c>
-      <c r="Q36" s="42">
+      <c r="Q37" s="42">
         <f t="shared" si="2"/>
         <v>1.3009999999999999</v>
       </c>
-      <c r="R36" s="35"/>
-      <c r="S36" s="64"/>
-    </row>
-    <row r="37" spans="1:19">
-      <c r="A37" s="2"/>
-      <c r="B37" s="36">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="38" t="s">
+      <c r="R37" s="35"/>
+      <c r="S37" s="64"/>
+    </row>
+    <row r="38" spans="1:19">
+      <c r="A38" s="2"/>
+      <c r="B38" s="36">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" s="37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>181</v>
+      </c>
+      <c r="G38" s="37">
+        <v>8266292</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="I38" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="E37" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="F37" s="37" t="s">
-        <v>186</v>
-      </c>
-      <c r="G37" s="37">
-        <v>8266292</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>187</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="K37" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L37" s="37">
+      <c r="K38" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" s="37">
         <v>1</v>
       </c>
-      <c r="M37" s="37">
+      <c r="M38" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N38" s="37">
         <v>6</v>
       </c>
-      <c r="O37" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P37" s="44">
+      <c r="O38" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="44">
         <v>0.3165</v>
       </c>
-      <c r="Q37" s="44">
+      <c r="Q38" s="44">
         <f t="shared" si="2"/>
         <v>1.899</v>
       </c>
-      <c r="R37" s="37"/>
-      <c r="S37" s="37"/>
-    </row>
-    <row r="38" spans="1:19">
-      <c r="A38" s="2"/>
-      <c r="B38" s="33">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C38" s="34" t="s">
+      <c r="R38" s="37"/>
+      <c r="S38" s="37"/>
+    </row>
+    <row r="39" spans="1:19">
+      <c r="A39" s="2"/>
+      <c r="B39" s="33">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="35" t="s">
         <v>189</v>
       </c>
-      <c r="D38" s="35" t="s">
+      <c r="K39" s="35" t="s">
         <v>190</v>
       </c>
-      <c r="E38" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="F38" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="G38" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="H38" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J38" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="K38" s="35" t="s">
-        <v>195</v>
-      </c>
-      <c r="L38" s="35">
+      <c r="L39" s="35">
         <v>1</v>
       </c>
-      <c r="M38" s="35">
+      <c r="M39" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N38" s="35">
+      <c r="N39" s="35">
         <v>10</v>
       </c>
-      <c r="O38" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P38" s="42">
+      <c r="O39" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P39" s="42">
         <v>0.2006</v>
       </c>
-      <c r="Q38" s="42">
+      <c r="Q39" s="42">
         <f t="shared" si="2"/>
         <v>2.0060000000000002</v>
       </c>
-      <c r="R38" s="35"/>
-      <c r="S38" s="64"/>
-    </row>
-    <row r="39" spans="1:19">
-      <c r="A39" s="2"/>
-      <c r="B39" s="36">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C39" s="38" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="37" t="s">
+      <c r="R39" s="35"/>
+      <c r="S39" s="64"/>
+    </row>
+    <row r="40" spans="1:19">
+      <c r="A40" s="2"/>
+      <c r="B40" s="36">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="K40" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="E39" s="37" t="s">
-        <v>197</v>
-      </c>
-      <c r="F39" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="H39" s="37" t="s">
-        <v>199</v>
-      </c>
-      <c r="I39" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="37" t="s">
-        <v>200</v>
-      </c>
-      <c r="K39" s="37" t="s">
-        <v>201</v>
-      </c>
-      <c r="L39" s="37">
+      <c r="L40" s="37">
         <v>1</v>
       </c>
-      <c r="M39" s="37">
+      <c r="M40" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N39" s="37">
+      <c r="N40" s="37">
         <v>10</v>
       </c>
-      <c r="O39" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P39" s="44">
+      <c r="O40" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P40" s="44">
         <v>6.6799999999999998E-2</v>
       </c>
-      <c r="Q39" s="44">
+      <c r="Q40" s="44">
         <f t="shared" si="2"/>
         <v>0.66799999999999993</v>
       </c>
-      <c r="R39" s="37"/>
-      <c r="S39" s="37"/>
-    </row>
-    <row r="40" spans="1:19" ht="36">
-      <c r="A40" s="2"/>
-      <c r="B40" s="33">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="D40" s="35" t="s">
+      <c r="R40" s="37"/>
+      <c r="S40" s="37"/>
+    </row>
+    <row r="41" spans="1:19" ht="36">
+      <c r="A41" s="2"/>
+      <c r="B41" s="33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="K41" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="E40" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="K40" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="L40" s="35">
+      <c r="L41" s="35">
         <v>1</v>
       </c>
-      <c r="M40" s="35">
+      <c r="M41" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N40" s="35">
+      <c r="N41" s="35">
         <v>10</v>
       </c>
-      <c r="O40" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P40" s="42">
+      <c r="O41" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P41" s="42">
         <v>0.1326</v>
       </c>
-      <c r="Q40" s="42">
+      <c r="Q41" s="42">
         <f t="shared" si="2"/>
         <v>1.3260000000000001</v>
       </c>
-      <c r="R40" s="35"/>
-      <c r="S40" s="64"/>
-    </row>
-    <row r="41" spans="1:19" ht="24">
-      <c r="A41" s="2"/>
-      <c r="B41" s="36">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="38" t="s">
+      <c r="R41" s="35"/>
+      <c r="S41" s="64"/>
+    </row>
+    <row r="42" spans="1:19" ht="24">
+      <c r="A42" s="2"/>
+      <c r="B42" s="36">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H42" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="D41" s="37" t="s">
+      <c r="I42" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="E41" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="K41" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L41" s="37">
+      <c r="K42" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L42" s="37">
         <v>1</v>
       </c>
-      <c r="M41" s="37">
+      <c r="M42" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N41" s="37">
+      <c r="N42" s="37">
         <v>20</v>
       </c>
-      <c r="O41" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P41" s="44">
+      <c r="O42" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P42" s="44">
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="Q41" s="44">
+      <c r="Q42" s="44">
         <f t="shared" si="2"/>
         <v>0.41599999999999998</v>
       </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-    </row>
-    <row r="42" spans="1:19" ht="48">
-      <c r="A42" s="2"/>
-      <c r="B42" s="33">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="C42" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="D42" s="35" t="s">
+      <c r="R42" s="37"/>
+      <c r="S42" s="37"/>
+    </row>
+    <row r="43" spans="1:19" ht="48">
+      <c r="A43" s="2"/>
+      <c r="B43" s="33">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="E42" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="F42" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="G42" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>219</v>
-      </c>
-      <c r="I42" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J42" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="K42" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L42" s="35">
+      <c r="K43" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="35">
         <v>1</v>
       </c>
-      <c r="M42" s="35">
+      <c r="M43" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N42" s="35">
+      <c r="N43" s="35">
         <v>100</v>
       </c>
-      <c r="O42" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P42" s="42">
+      <c r="O43" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P43" s="42">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="Q42" s="42">
+      <c r="Q43" s="42">
         <f t="shared" si="2"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="R42" s="35"/>
-      <c r="S42" s="64"/>
-    </row>
-    <row r="43" spans="1:19">
-      <c r="A43" s="2"/>
-      <c r="B43" s="36">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>221</v>
-      </c>
-      <c r="D43" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="E43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="G43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="K43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" s="39">
+      <c r="R43" s="35"/>
+      <c r="S43" s="64"/>
+    </row>
+    <row r="44" spans="1:19">
+      <c r="A44" s="2"/>
+      <c r="B44" s="36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="39">
         <v>1</v>
       </c>
-      <c r="M43" s="39">
+      <c r="M44" s="39">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P43" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q43" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R43" s="39"/>
-      <c r="S43" s="37"/>
-    </row>
-    <row r="44" spans="1:19" ht="36">
-      <c r="A44" s="2"/>
-      <c r="B44" s="33">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="34" t="s">
+      <c r="N44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q44" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R44" s="39"/>
+      <c r="S44" s="37"/>
+    </row>
+    <row r="45" spans="1:19" ht="36">
+      <c r="A45" s="2"/>
+      <c r="B45" s="33">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="G45" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="H45" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="I45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="E44" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="F44" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="G44" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="H44" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J44" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="K44" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L44" s="35">
+      <c r="K45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L45" s="35">
         <v>1</v>
       </c>
-      <c r="M44" s="35">
+      <c r="M45" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N44" s="35">
+      <c r="N45" s="35">
         <v>20</v>
       </c>
-      <c r="O44" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P44" s="42">
+      <c r="O45" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P45" s="42">
         <v>3.04E-2</v>
       </c>
-      <c r="Q44" s="42">
+      <c r="Q45" s="42">
         <f t="shared" si="2"/>
         <v>0.60799999999999998</v>
       </c>
-      <c r="R44" s="35"/>
-      <c r="S44" s="64"/>
-    </row>
-    <row r="45" spans="1:19" ht="48">
-      <c r="A45" s="2"/>
-      <c r="B45" s="36">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="D45" s="37" t="s">
+      <c r="R45" s="35"/>
+      <c r="S45" s="64"/>
+    </row>
+    <row r="46" spans="1:19" ht="48">
+      <c r="A46" s="2"/>
+      <c r="B46" s="36">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="37" t="s">
         <v>231</v>
       </c>
-      <c r="E45" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="I45" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="37" t="s">
-        <v>236</v>
-      </c>
-      <c r="K45" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L45" s="37">
+      <c r="K46" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" s="37">
         <v>1</v>
       </c>
-      <c r="M45" s="37">
+      <c r="M46" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N45" s="37">
+      <c r="N46" s="37">
         <v>20</v>
       </c>
-      <c r="O45" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P45" s="44">
+      <c r="O46" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P46" s="44">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="Q45" s="44">
+      <c r="Q46" s="44">
         <f t="shared" si="2"/>
         <v>0.67</v>
       </c>
-      <c r="R45" s="37"/>
-      <c r="S45" s="37"/>
-    </row>
-    <row r="46" spans="1:19">
-      <c r="A46" s="2"/>
-      <c r="B46" s="33">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="38" t="s">
+      <c r="R46" s="37"/>
+      <c r="S46" s="37"/>
+    </row>
+    <row r="47" spans="1:19">
+      <c r="A47" s="2"/>
+      <c r="B47" s="33">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="G47" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="K47" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="E46" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="F46" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="G46" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="K46" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="L46" s="35">
+      <c r="L47" s="35">
         <v>2</v>
       </c>
-      <c r="M46" s="35">
+      <c r="M47" s="35">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N46" s="35">
+      <c r="N47" s="35">
         <v>100</v>
       </c>
-      <c r="O46" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P46" s="42">
+      <c r="O47" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P47" s="42">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="Q46" s="42">
+      <c r="Q47" s="42">
         <f t="shared" si="2"/>
         <v>0.08</v>
       </c>
-      <c r="R46" s="35"/>
-      <c r="S46" s="64"/>
-    </row>
-    <row r="47" spans="1:19">
-      <c r="A47" s="2"/>
-      <c r="B47" s="36">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D47" s="37" t="s">
+      <c r="R47" s="35"/>
+      <c r="S47" s="64"/>
+    </row>
+    <row r="48" spans="1:19">
+      <c r="A48" s="2"/>
+      <c r="B48" s="36">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" s="37" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="F48" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="H48" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="K48" s="37" t="s">
         <v>244</v>
       </c>
-      <c r="E47" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="G47" s="37" t="s">
-        <v>247</v>
-      </c>
-      <c r="H47" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="K47" s="37" t="s">
-        <v>249</v>
-      </c>
-      <c r="L47" s="37">
+      <c r="L48" s="37">
         <v>2</v>
       </c>
-      <c r="M47" s="37">
+      <c r="M48" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N47" s="37">
+      <c r="N48" s="37">
         <v>20</v>
       </c>
-      <c r="O47" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P47" s="44">
+      <c r="O48" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P48" s="44">
         <v>2.1700000000000001E-2</v>
       </c>
-      <c r="Q47" s="44">
+      <c r="Q48" s="44">
         <f t="shared" si="2"/>
         <v>0.434</v>
       </c>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
-    </row>
-    <row r="48" spans="1:19">
-      <c r="A48" s="2"/>
-      <c r="B48" s="33">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D48" s="35" t="s">
+      <c r="R48" s="37"/>
+      <c r="S48" s="37"/>
+    </row>
+    <row r="49" spans="1:22">
+      <c r="A49" s="2"/>
+      <c r="B49" s="33">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C49" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="G49" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="H49" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="K49" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="E48" s="35" t="s">
-        <v>251</v>
-      </c>
-      <c r="F48" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="G48" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="H48" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="K48" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="L48" s="35">
+      <c r="L49" s="35">
         <v>5</v>
       </c>
-      <c r="M48" s="35">
+      <c r="M49" s="35">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="N48" s="35">
+      <c r="N49" s="35">
         <v>40</v>
       </c>
-      <c r="O48" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P48" s="42">
+      <c r="O49" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P49" s="42">
         <v>1.41E-2</v>
       </c>
-      <c r="Q48" s="42">
+      <c r="Q49" s="42">
         <f t="shared" si="2"/>
         <v>0.56399999999999995</v>
       </c>
-      <c r="R48" s="35"/>
-      <c r="S48" s="64"/>
-    </row>
-    <row r="49" spans="1:19">
-      <c r="A49" s="2"/>
-      <c r="B49" s="36">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="F49" s="37" t="s">
+      <c r="R49" s="35"/>
+      <c r="S49" s="64"/>
+    </row>
+    <row r="50" spans="1:22">
+      <c r="A50" s="2"/>
+      <c r="B50" s="36">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="G49" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="H49" s="37" t="s">
+      <c r="F50" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="H50" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="I49" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K49" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="L49" s="37">
+      <c r="I50" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="K50" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="L50" s="37">
         <v>2</v>
       </c>
-      <c r="M49" s="37">
+      <c r="M50" s="37">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N49" s="37">
+      <c r="N50" s="37">
         <v>100</v>
       </c>
-      <c r="O49" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P49" s="44">
+      <c r="O50" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P50" s="44">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q49" s="44">
+      <c r="Q50" s="44">
         <f t="shared" si="2"/>
         <v>0.06</v>
       </c>
-      <c r="R49" s="37"/>
-      <c r="S49" s="37"/>
-    </row>
-    <row r="50" spans="1:19">
-      <c r="A50" s="2"/>
-      <c r="B50" s="33">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D50" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="F50" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="G50" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="H50" s="35" t="s">
+      <c r="R50" s="37"/>
+      <c r="S50" s="37"/>
+    </row>
+    <row r="51" spans="1:22">
+      <c r="A51" s="2"/>
+      <c r="B51" s="33">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="H51" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="I50" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J50" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="K50" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="L50" s="35">
+      <c r="I51" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="K51" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="L51" s="35">
         <v>1</v>
       </c>
-      <c r="M50" s="35">
+      <c r="M51" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N50" s="35">
+      <c r="N51" s="35">
         <v>100</v>
       </c>
-      <c r="O50" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P50" s="42">
+      <c r="O51" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P51" s="42">
         <v>1E-3</v>
       </c>
-      <c r="Q50" s="42">
+      <c r="Q51" s="42">
         <f t="shared" si="2"/>
         <v>0.1</v>
       </c>
-      <c r="R50" s="35"/>
-      <c r="S50" s="64"/>
-    </row>
-    <row r="51" spans="1:19">
-      <c r="A51" s="2"/>
-      <c r="B51" s="36">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C51" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>267</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="H51" s="37" t="s">
+      <c r="R51" s="35"/>
+      <c r="S51" s="64"/>
+    </row>
+    <row r="52" spans="1:22">
+      <c r="A52" s="2"/>
+      <c r="B52" s="36">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="E52" s="37" t="s">
+        <v>262</v>
+      </c>
+      <c r="F52" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="H52" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="I51" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J51" s="37" t="s">
-        <v>269</v>
-      </c>
-      <c r="K51" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="L51" s="37">
+      <c r="I52" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="K52" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="L52" s="37">
         <v>3</v>
       </c>
-      <c r="M51" s="37">
+      <c r="M52" s="37">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N51" s="37">
+      <c r="N52" s="37">
         <v>100</v>
       </c>
-      <c r="O51" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P51" s="44">
+      <c r="O52" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P52" s="44">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q51" s="44">
+      <c r="Q52" s="44">
         <f t="shared" si="2"/>
         <v>0.11</v>
       </c>
-      <c r="R51" s="37"/>
-      <c r="S51" s="37"/>
-    </row>
-    <row r="52" spans="1:19" ht="36">
-      <c r="A52" s="2"/>
-      <c r="B52" s="33">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D52" s="35" t="s">
+      <c r="R52" s="37"/>
+      <c r="S52" s="37"/>
+    </row>
+    <row r="53" spans="1:22" ht="36">
+      <c r="A53" s="2"/>
+      <c r="B53" s="33">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="H53" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="K53" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="F52" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="G52" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="H52" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="K52" s="35" t="s">
-        <v>277</v>
-      </c>
-      <c r="L52" s="35">
+      <c r="L53" s="35">
         <v>3</v>
       </c>
-      <c r="M52" s="35">
+      <c r="M53" s="35">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="N52" s="35">
+      <c r="N53" s="35">
         <v>100</v>
       </c>
-      <c r="O52" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P52" s="42">
+      <c r="O53" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P53" s="42">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Q52" s="42">
+      <c r="Q53" s="42">
         <f t="shared" si="2"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="R52" s="35"/>
-      <c r="S52" s="64"/>
-    </row>
-    <row r="53" spans="1:19">
-      <c r="A53" s="2"/>
-      <c r="B53" s="36">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="H53" s="37" t="s">
+      <c r="R53" s="35"/>
+      <c r="S53" s="64"/>
+    </row>
+    <row r="54" spans="1:22">
+      <c r="A54" s="2"/>
+      <c r="B54" s="36">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="F54" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="G54" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="H54" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="I53" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J53" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="K53" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="L53" s="37">
+      <c r="I54" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="K54" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="L54" s="37">
         <v>1</v>
       </c>
-      <c r="M53" s="37">
+      <c r="M54" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N53" s="37">
+      <c r="N54" s="37">
         <v>100</v>
       </c>
-      <c r="O53" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P53" s="44">
+      <c r="O54" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P54" s="44">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q53" s="44">
+      <c r="Q54" s="44">
         <f t="shared" si="2"/>
         <v>0.12</v>
       </c>
-      <c r="R53" s="37"/>
-      <c r="S53" s="37"/>
-    </row>
-    <row r="54" spans="1:19">
-      <c r="A54" s="2"/>
-      <c r="B54" s="33">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D54" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="E54" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="F54" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="G54" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="H54" s="35" t="s">
+      <c r="R54" s="37"/>
+      <c r="S54" s="37"/>
+    </row>
+    <row r="55" spans="1:22">
+      <c r="A55" s="2"/>
+      <c r="B55" s="33">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="G55" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="H55" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="I54" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J54" s="35" t="s">
-        <v>286</v>
-      </c>
-      <c r="K54" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="L54" s="35">
+      <c r="I55" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J55" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="K55" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="L55" s="35">
         <v>1</v>
       </c>
-      <c r="M54" s="35">
+      <c r="M55" s="35">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N54" s="35">
+      <c r="N55" s="35">
         <v>100</v>
       </c>
-      <c r="O54" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P54" s="42">
+      <c r="O55" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P55" s="42">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="Q54" s="42">
+      <c r="Q55" s="42">
         <f t="shared" si="2"/>
         <v>0.21</v>
       </c>
-      <c r="R54" s="35"/>
-      <c r="S54" s="64"/>
-    </row>
-    <row r="55" spans="1:19">
-      <c r="A55" s="2"/>
-      <c r="B55" s="36">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>289</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>290</v>
-      </c>
-      <c r="H55" s="37" t="s">
+      <c r="R55" s="35"/>
+      <c r="S55" s="64"/>
+    </row>
+    <row r="56" spans="1:22">
+      <c r="A56" s="2"/>
+      <c r="B56" s="36">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>283</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="F56" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="G56" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="H56" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="I55" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J55" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="K55" s="37" t="s">
-        <v>292</v>
-      </c>
-      <c r="L55" s="37">
+      <c r="I56" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="K56" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="L56" s="37">
         <v>1</v>
       </c>
-      <c r="M55" s="37">
+      <c r="M56" s="37">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="N55" s="37">
+      <c r="N56" s="37">
         <v>20</v>
       </c>
-      <c r="O55" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P55" s="44">
+      <c r="O56" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P56" s="44">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="Q55" s="44">
+      <c r="Q56" s="44">
         <f t="shared" si="2"/>
         <v>0.75</v>
       </c>
-      <c r="R55" s="37"/>
-      <c r="S55" s="37"/>
-    </row>
-    <row r="56" spans="1:19">
-      <c r="A56" s="2"/>
-      <c r="B56" s="33">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="C56" s="34" t="s">
+      <c r="R56" s="37"/>
+      <c r="S56" s="37"/>
+    </row>
+    <row r="57" spans="1:22">
+      <c r="A57" s="2"/>
+      <c r="B57" s="36">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C57" s="94" t="s">
+        <v>232</v>
+      </c>
+      <c r="D57" s="93" t="s">
+        <v>377</v>
+      </c>
+      <c r="E57" s="93" t="s">
+        <v>378</v>
+      </c>
+      <c r="F57" s="93" t="s">
+        <v>241</v>
+      </c>
+      <c r="G57" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="H57" s="93" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" s="93" t="s">
+        <v>381</v>
+      </c>
+      <c r="J57" s="93" t="s">
+        <v>382</v>
+      </c>
+      <c r="K57" s="93" t="s">
+        <v>380</v>
+      </c>
+      <c r="L57" s="35">
+        <v>1</v>
+      </c>
+      <c r="M57" s="35">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="N57" s="35">
+        <v>100</v>
+      </c>
+      <c r="O57" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P57" s="42">
+        <v>1E-3</v>
+      </c>
+      <c r="Q57" s="44">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
+    </row>
+    <row r="58" spans="1:22">
+      <c r="A58" s="2"/>
+      <c r="B58" s="33">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="E58" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="F58" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="G58" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="H58" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="I58" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J58" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="D56" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="E56" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="F56" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="G56" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="H56" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="I56" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J56" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="K56" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" s="35">
+      <c r="K58" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L58" s="35">
         <v>2</v>
       </c>
-      <c r="M56" s="35">
+      <c r="M58" s="35">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="N56" s="35">
+      <c r="N58" s="35">
         <v>15</v>
       </c>
-      <c r="O56" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P56" s="42">
+      <c r="O58" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P58" s="42">
         <v>0.1729</v>
       </c>
-      <c r="Q56" s="42">
+      <c r="Q58" s="42">
         <f t="shared" si="2"/>
         <v>2.5935000000000001</v>
       </c>
-      <c r="R56" s="35"/>
-      <c r="S56" s="64"/>
-    </row>
-    <row r="57" spans="1:19" s="1" customFormat="1">
-      <c r="A57" s="32"/>
-      <c r="B57" s="36">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="C57" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="K57" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L57" s="37">
-        <v>1</v>
-      </c>
-      <c r="M57" s="37">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N57" s="37">
-        <v>6</v>
-      </c>
-      <c r="O57" s="43" t="s">
-        <v>316</v>
-      </c>
-      <c r="P57" s="44">
-        <v>16.25</v>
-      </c>
-      <c r="Q57" s="44">
-        <f t="shared" si="2"/>
-        <v>97.5</v>
-      </c>
-      <c r="R57" s="37"/>
-      <c r="S57" s="37"/>
-    </row>
-    <row r="58" spans="1:19">
-      <c r="A58" s="2"/>
-      <c r="B58" s="33">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="C58" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>305</v>
-      </c>
-      <c r="E58" s="35" t="s">
-        <v>306</v>
-      </c>
-      <c r="F58" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="G58" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="H58" s="35" t="s">
-        <v>309</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J58" s="35" t="s">
-        <v>310</v>
-      </c>
-      <c r="K58" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L58" s="35">
-        <v>1</v>
-      </c>
-      <c r="M58" s="35">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="N58" s="35">
-        <v>6</v>
-      </c>
-      <c r="O58" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P58" s="42">
-        <v>0.81299999999999994</v>
-      </c>
-      <c r="Q58" s="42">
-        <f t="shared" si="2"/>
-        <v>4.8780000000000001</v>
-      </c>
       <c r="R58" s="35"/>
       <c r="S58" s="64"/>
     </row>
-    <row r="59" spans="1:19">
-      <c r="A59" s="2"/>
+    <row r="59" spans="1:22" s="1" customFormat="1">
+      <c r="A59" s="32"/>
       <c r="B59" s="36">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="C59" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="H59" s="37" t="s">
         <v>299</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="I59" s="37" t="s">
         <v>31</v>
@@ -5298,47 +5358,49 @@
         <v>6</v>
       </c>
       <c r="O59" s="43" t="s">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="P59" s="44">
-        <v>6.25</v>
+        <v>16.25</v>
       </c>
       <c r="Q59" s="44">
         <f t="shared" si="2"/>
-        <v>37.5</v>
+        <v>97.5</v>
       </c>
       <c r="R59" s="37"/>
       <c r="S59" s="37"/>
-    </row>
-    <row r="60" spans="1:19">
+      <c r="U59"/>
+      <c r="V59"/>
+    </row>
+    <row r="60" spans="1:22">
       <c r="A60" s="2"/>
       <c r="B60" s="33">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D60" s="35" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="E60" s="35" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="F60" s="35" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="G60" s="35" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="H60" s="35" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="I60" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J60" s="35" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="K60" s="35" t="s">
         <v>31</v>
@@ -5357,100 +5419,104 @@
         <v>34</v>
       </c>
       <c r="P60" s="42">
-        <v>0.34710000000000002</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="Q60" s="42">
         <f t="shared" si="2"/>
-        <v>2.0826000000000002</v>
+        <v>4.8780000000000001</v>
       </c>
       <c r="R60" s="35"/>
       <c r="S60" s="64"/>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:22">
       <c r="A61" s="2"/>
       <c r="B61" s="36">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="38" t="s">
-        <v>299</v>
+      <c r="C61" s="34" t="s">
+        <v>294</v>
       </c>
       <c r="D61" s="37" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="I61" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J61" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="K61" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="K61" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="L61" s="37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M61" s="37">
         <f t="shared" si="1"/>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="N61" s="37">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O61" s="43" t="s">
-        <v>34</v>
+        <v>365</v>
       </c>
       <c r="P61" s="44">
-        <v>0.67620000000000002</v>
+        <v>6.25</v>
       </c>
       <c r="Q61" s="44">
         <f t="shared" si="2"/>
-        <v>10.8192</v>
+        <v>37.5</v>
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="37"/>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:22">
       <c r="A62" s="2"/>
       <c r="B62" s="33">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="G62" s="35" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="I62" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J62" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="K62" s="35"/>
+        <v>317</v>
+      </c>
+      <c r="K62" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="L62" s="35">
         <v>1</v>
       </c>
@@ -5465,98 +5531,98 @@
         <v>34</v>
       </c>
       <c r="P62" s="42">
-        <v>0.4073</v>
+        <v>0.34710000000000002</v>
       </c>
       <c r="Q62" s="42">
         <f t="shared" si="2"/>
-        <v>2.4438</v>
+        <v>2.0826000000000002</v>
       </c>
       <c r="R62" s="35"/>
       <c r="S62" s="64"/>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:22">
       <c r="A63" s="2"/>
       <c r="B63" s="36">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="E63" s="37" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="I63" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J63" s="37" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="K63" s="37"/>
       <c r="L63" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M63" s="37">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="N63" s="37">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O63" s="43" t="s">
         <v>34</v>
       </c>
       <c r="P63" s="44">
-        <v>0.16880000000000001</v>
+        <v>0.67620000000000002</v>
       </c>
       <c r="Q63" s="44">
         <f t="shared" si="2"/>
-        <v>1.6880000000000002</v>
+        <v>10.8192</v>
       </c>
       <c r="R63" s="37"/>
       <c r="S63" s="37"/>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:22">
       <c r="A64" s="2"/>
       <c r="B64" s="33">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D64" s="35" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="E64" s="35" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="F64" s="35" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="G64" s="35" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="H64" s="35" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I64" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J64" s="35" t="s">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="K64" s="35"/>
       <c r="L64" s="35">
@@ -5573,48 +5639,46 @@
         <v>34</v>
       </c>
       <c r="P64" s="42">
-        <v>1.0866</v>
+        <v>0.4073</v>
       </c>
       <c r="Q64" s="42">
         <f t="shared" si="2"/>
-        <v>6.5196000000000005</v>
+        <v>2.4438</v>
       </c>
       <c r="R64" s="35"/>
       <c r="S64" s="64"/>
     </row>
-    <row r="65" spans="1:19" ht="36">
+    <row r="65" spans="1:19">
       <c r="A65" s="2"/>
       <c r="B65" s="36">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>346</v>
+        <v>294</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="I65" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="K65" s="37" t="s">
-        <v>352</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="K65" s="37"/>
       <c r="L65" s="37">
         <v>1</v>
       </c>
@@ -5629,48 +5693,46 @@
         <v>34</v>
       </c>
       <c r="P65" s="44">
-        <v>6.6100000000000006E-2</v>
+        <v>0.16880000000000001</v>
       </c>
       <c r="Q65" s="44">
         <f t="shared" si="2"/>
-        <v>0.66100000000000003</v>
+        <v>1.6880000000000002</v>
       </c>
       <c r="R65" s="37"/>
       <c r="S65" s="37"/>
     </row>
-    <row r="66" spans="1:19" ht="24">
+    <row r="66" spans="1:19">
       <c r="A66" s="2"/>
       <c r="B66" s="33">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="38" t="s">
-        <v>346</v>
+      <c r="C66" s="34" t="s">
+        <v>294</v>
       </c>
       <c r="D66" s="35" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E66" s="35" t="s">
-        <v>354</v>
-      </c>
-      <c r="F66" s="37" t="s">
-        <v>173</v>
+        <v>337</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>338</v>
       </c>
       <c r="G66" s="35" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="H66" s="35" t="s">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="I66" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J66" s="35" t="s">
-        <v>357</v>
-      </c>
-      <c r="K66" s="35" t="s">
-        <v>358</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="K66" s="35"/>
       <c r="L66" s="35">
         <v>1</v>
       </c>
@@ -5679,103 +5741,109 @@
         <v>5</v>
       </c>
       <c r="N66" s="35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O66" s="41" t="s">
         <v>34</v>
       </c>
       <c r="P66" s="42">
-        <v>0.1401</v>
+        <v>1.0866</v>
       </c>
       <c r="Q66" s="42">
         <f t="shared" si="2"/>
-        <v>1.401</v>
+        <v>6.5196000000000005</v>
       </c>
       <c r="R66" s="35"/>
       <c r="S66" s="64"/>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" ht="36">
       <c r="A67" s="2"/>
-      <c r="B67" s="33">
+      <c r="B67" s="36">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E67" s="35" t="s">
-        <v>365</v>
+        <v>341</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>343</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G67" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>31</v>
+        <v>168</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>345</v>
       </c>
       <c r="I67" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J67" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K67" s="35"/>
-      <c r="L67" s="35">
+      <c r="J67" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="K67" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="L67" s="37">
+        <v>1</v>
+      </c>
+      <c r="M67" s="37">
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M67" s="35">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="N67" s="35">
-        <v>26</v>
-      </c>
-      <c r="O67" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P67" s="42">
-        <v>7.5</v>
-      </c>
-      <c r="Q67" s="42">
+      <c r="N67" s="37">
+        <v>10</v>
+      </c>
+      <c r="O67" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P67" s="44">
+        <v>6.6100000000000006E-2</v>
+      </c>
+      <c r="Q67" s="44">
         <f t="shared" si="2"/>
-        <v>195</v>
-      </c>
-      <c r="R67" s="35"/>
-      <c r="S67" s="64"/>
-    </row>
-    <row r="68" spans="1:19">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="R67" s="37"/>
+      <c r="S67" s="37"/>
+    </row>
+    <row r="68" spans="1:19" ht="24">
       <c r="A68" s="2"/>
       <c r="B68" s="33">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="C68" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D68" s="35"/>
+        <v>341</v>
+      </c>
+      <c r="D68" s="35" t="s">
+        <v>348</v>
+      </c>
       <c r="E68" s="35" t="s">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="F68" s="37" t="s">
-        <v>31</v>
+        <v>168</v>
       </c>
       <c r="G68" s="35" t="s">
-        <v>368</v>
+        <v>350</v>
       </c>
       <c r="H68" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="37"/>
+        <v>351</v>
+      </c>
+      <c r="I68" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="J68" s="35" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="K68" s="35" t="s">
-        <v>31</v>
+        <v>353</v>
       </c>
       <c r="L68" s="35">
         <v>1</v>
@@ -5785,117 +5853,227 @@
         <v>5</v>
       </c>
       <c r="N68" s="35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O68" s="41" t="s">
         <v>34</v>
       </c>
       <c r="P68" s="42">
-        <v>0.2069</v>
+        <v>0.1401</v>
       </c>
       <c r="Q68" s="42">
         <f t="shared" si="2"/>
-        <v>1.2414000000000001</v>
+        <v>1.401</v>
       </c>
       <c r="R68" s="35"/>
       <c r="S68" s="64"/>
     </row>
-    <row r="69" spans="1:19" ht="15.75" thickBot="1">
+    <row r="69" spans="1:19">
       <c r="A69" s="2"/>
       <c r="B69" s="33">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D69" s="35"/>
+        <v>359</v>
+      </c>
+      <c r="D69" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="E69" s="35" t="s">
-        <v>372</v>
-      </c>
-      <c r="F69" s="37"/>
+        <v>360</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="G69" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="H69" s="35"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="35"/>
+        <v>361</v>
+      </c>
+      <c r="H69" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="K69" s="35"/>
       <c r="L69" s="35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69" s="35">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N69" s="35">
-        <v>30</v>
-      </c>
-      <c r="O69" s="41"/>
-      <c r="P69" s="42"/>
-      <c r="Q69" s="42"/>
+        <v>26</v>
+      </c>
+      <c r="O69" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P69" s="42">
+        <v>7.5</v>
+      </c>
+      <c r="Q69" s="42">
+        <f t="shared" si="2"/>
+        <v>195</v>
+      </c>
       <c r="R69" s="35"/>
       <c r="S69" s="64"/>
     </row>
-    <row r="70" spans="1:19" ht="19.5" thickBot="1">
+    <row r="70" spans="1:19">
       <c r="A70" s="2"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="52"/>
-      <c r="D70" s="53"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="56"/>
-      <c r="H70" s="55"/>
-      <c r="I70" s="56"/>
-      <c r="J70" s="55"/>
-      <c r="K70" s="56"/>
-      <c r="L70" s="56"/>
-      <c r="M70" s="56"/>
-      <c r="N70" s="85" t="s">
+      <c r="B70" s="33">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C70" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="O70" s="86"/>
-      <c r="P70" s="86"/>
-      <c r="Q70" s="61">
-        <f>SUM(Q10:Q69)</f>
-        <v>397.50710000000004</v>
-      </c>
-      <c r="R70" s="89"/>
-      <c r="S70" s="90"/>
-    </row>
-    <row r="71" spans="1:19" ht="18.75">
+      <c r="D70" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="95" t="s">
+        <v>384</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="95" t="s">
+        <v>383</v>
+      </c>
+      <c r="H70" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L70" s="35">
+        <v>1</v>
+      </c>
+      <c r="M70" s="35">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="N70" s="35">
+        <v>6</v>
+      </c>
+      <c r="O70" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="P70" s="42">
+        <v>1.32</v>
+      </c>
+      <c r="Q70" s="42">
+        <f t="shared" si="2"/>
+        <v>7.92</v>
+      </c>
+      <c r="R70" s="35"/>
+      <c r="S70" s="64"/>
+    </row>
+    <row r="71" spans="1:19" ht="15.75" thickBot="1">
       <c r="A71" s="2"/>
-      <c r="B71" s="57"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="60"/>
-      <c r="K71" s="60"/>
-      <c r="L71" s="60"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="85" t="s">
-        <v>360</v>
-      </c>
-      <c r="O71" s="86"/>
-      <c r="P71" s="86"/>
-      <c r="Q71" s="62">
-        <f>Q70/5</f>
-        <v>79.50142000000001</v>
-      </c>
-      <c r="R71" s="91"/>
-      <c r="S71" s="92"/>
+      <c r="B71" s="33">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C71" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="D71" s="35"/>
+      <c r="E71" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="F71" s="37"/>
+      <c r="G71" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="H71" s="35"/>
+      <c r="I71" s="37"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
+      <c r="L71" s="35">
+        <v>6</v>
+      </c>
+      <c r="M71" s="35">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N71" s="35">
+        <v>30</v>
+      </c>
+      <c r="O71" s="41"/>
+      <c r="P71" s="42"/>
+      <c r="Q71" s="42"/>
+      <c r="R71" s="35"/>
+      <c r="S71" s="64"/>
+    </row>
+    <row r="72" spans="1:19" ht="19.5" thickBot="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="56"/>
+      <c r="L72" s="56"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="85" t="s">
+        <v>354</v>
+      </c>
+      <c r="O72" s="86"/>
+      <c r="P72" s="86"/>
+      <c r="Q72" s="61">
+        <f>SUM(Q10:Q71)</f>
+        <v>404.92770000000002</v>
+      </c>
+      <c r="R72" s="89"/>
+      <c r="S72" s="90"/>
+    </row>
+    <row r="73" spans="1:19" ht="18.75">
+      <c r="A73" s="2"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="60"/>
+      <c r="K73" s="60"/>
+      <c r="L73" s="60"/>
+      <c r="M73" s="60"/>
+      <c r="N73" s="85" t="s">
+        <v>355</v>
+      </c>
+      <c r="O73" s="86"/>
+      <c r="P73" s="86"/>
+      <c r="Q73" s="62">
+        <f>Q72/5</f>
+        <v>80.98554</v>
+      </c>
+      <c r="R73" s="91"/>
+      <c r="S73" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="N73:P73"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R70:S71"/>
+    <mergeCell ref="R72:S73"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -5914,56 +6092,58 @@
     <hyperlink ref="O23" r:id="rId14"/>
     <hyperlink ref="O24" r:id="rId15"/>
     <hyperlink ref="O25" r:id="rId16"/>
-    <hyperlink ref="O27" r:id="rId17"/>
-    <hyperlink ref="O28" r:id="rId18"/>
-    <hyperlink ref="O29" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O31" r:id="rId21"/>
-    <hyperlink ref="O32" r:id="rId22"/>
-    <hyperlink ref="O35" r:id="rId23"/>
-    <hyperlink ref="O36" r:id="rId24"/>
-    <hyperlink ref="O37" r:id="rId25"/>
-    <hyperlink ref="O38" r:id="rId26"/>
-    <hyperlink ref="O39" r:id="rId27"/>
-    <hyperlink ref="O40" r:id="rId28"/>
-    <hyperlink ref="O41" r:id="rId29"/>
-    <hyperlink ref="O42" r:id="rId30"/>
-    <hyperlink ref="O44" r:id="rId31"/>
-    <hyperlink ref="O45" r:id="rId32"/>
-    <hyperlink ref="O46" r:id="rId33"/>
-    <hyperlink ref="O47" r:id="rId34"/>
-    <hyperlink ref="O48" r:id="rId35"/>
-    <hyperlink ref="O49" r:id="rId36"/>
-    <hyperlink ref="O50" r:id="rId37"/>
-    <hyperlink ref="O51" r:id="rId38"/>
-    <hyperlink ref="O52" r:id="rId39"/>
-    <hyperlink ref="O53" r:id="rId40"/>
-    <hyperlink ref="O54" r:id="rId41"/>
-    <hyperlink ref="O55" r:id="rId42"/>
-    <hyperlink ref="O56" r:id="rId43"/>
-    <hyperlink ref="O58" r:id="rId44"/>
-    <hyperlink ref="O60" r:id="rId45"/>
-    <hyperlink ref="O61" r:id="rId46"/>
-    <hyperlink ref="O62" r:id="rId47"/>
-    <hyperlink ref="O63" r:id="rId48"/>
-    <hyperlink ref="O64" r:id="rId49"/>
-    <hyperlink ref="O65" r:id="rId50"/>
-    <hyperlink ref="O66" r:id="rId51"/>
-    <hyperlink ref="O26" r:id="rId52"/>
-    <hyperlink ref="O67" r:id="rId53"/>
-    <hyperlink ref="O68" r:id="rId54"/>
-    <hyperlink ref="O59" r:id="rId55"/>
-    <hyperlink ref="O57" r:id="rId56"/>
+    <hyperlink ref="O28" r:id="rId17"/>
+    <hyperlink ref="O29" r:id="rId18"/>
+    <hyperlink ref="O30" r:id="rId19"/>
+    <hyperlink ref="O32" r:id="rId20"/>
+    <hyperlink ref="O33" r:id="rId21"/>
+    <hyperlink ref="O36" r:id="rId22"/>
+    <hyperlink ref="O37" r:id="rId23"/>
+    <hyperlink ref="O38" r:id="rId24"/>
+    <hyperlink ref="O39" r:id="rId25"/>
+    <hyperlink ref="O40" r:id="rId26"/>
+    <hyperlink ref="O41" r:id="rId27"/>
+    <hyperlink ref="O42" r:id="rId28"/>
+    <hyperlink ref="O43" r:id="rId29"/>
+    <hyperlink ref="O45" r:id="rId30"/>
+    <hyperlink ref="O46" r:id="rId31"/>
+    <hyperlink ref="O47" r:id="rId32"/>
+    <hyperlink ref="O48" r:id="rId33"/>
+    <hyperlink ref="O49" r:id="rId34"/>
+    <hyperlink ref="O50" r:id="rId35"/>
+    <hyperlink ref="O51" r:id="rId36"/>
+    <hyperlink ref="O52" r:id="rId37"/>
+    <hyperlink ref="O53" r:id="rId38"/>
+    <hyperlink ref="O54" r:id="rId39"/>
+    <hyperlink ref="O55" r:id="rId40"/>
+    <hyperlink ref="O56" r:id="rId41"/>
+    <hyperlink ref="O58" r:id="rId42"/>
+    <hyperlink ref="O60" r:id="rId43"/>
+    <hyperlink ref="O62" r:id="rId44"/>
+    <hyperlink ref="O63" r:id="rId45"/>
+    <hyperlink ref="O64" r:id="rId46"/>
+    <hyperlink ref="O65" r:id="rId47"/>
+    <hyperlink ref="O66" r:id="rId48"/>
+    <hyperlink ref="O67" r:id="rId49"/>
+    <hyperlink ref="O68" r:id="rId50"/>
+    <hyperlink ref="O26" r:id="rId51"/>
+    <hyperlink ref="O69" r:id="rId52"/>
+    <hyperlink ref="O61" r:id="rId53"/>
+    <hyperlink ref="O59" r:id="rId54"/>
+    <hyperlink ref="O27" r:id="rId55"/>
+    <hyperlink ref="O31" r:id="rId56"/>
+    <hyperlink ref="O57" r:id="rId57"/>
+    <hyperlink ref="O70" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId57"/>
+  <drawing r:id="rId59"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S71"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.7109375" customWidth="1"/>
@@ -6209,16 +6389,16 @@
         <v>18</v>
       </c>
       <c r="N9" s="31" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O9" s="31" t="s">
         <v>20</v>
       </c>
       <c r="P9" s="31" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Q9" s="31" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="R9" s="31" t="s">
         <v>23</v>
@@ -6230,7 +6410,7 @@
     <row r="10" spans="1:19" s="1" customFormat="1">
       <c r="A10" s="32"/>
       <c r="B10" s="33">
-        <f t="shared" ref="B10:B69" si="0">ROW(B10)-ROW($B$9)</f>
+        <f t="shared" ref="B10:B71" si="0">ROW(B10)-ROW($B$9)</f>
         <v>1</v>
       </c>
       <c r="C10" s="34" t="s">
@@ -6277,7 +6457,7 @@
         <v>4.1000000000000003E-3</v>
       </c>
       <c r="Q10" s="42">
-        <f t="shared" ref="Q10:Q32" si="1">P10*N10</f>
+        <f t="shared" ref="Q10:Q33" si="1">P10*N10</f>
         <v>0.41000000000000003</v>
       </c>
       <c r="R10" s="35"/>
@@ -6320,7 +6500,7 @@
         <v>19</v>
       </c>
       <c r="M11" s="35">
-        <f t="shared" ref="M11:M42" si="2">L11*10</f>
+        <f t="shared" ref="M11:M43" si="2">L11*10</f>
         <v>190</v>
       </c>
       <c r="N11" s="37">
@@ -7179,8 +7359,8 @@
       <c r="R26" s="35"/>
       <c r="S26" s="49"/>
     </row>
-    <row r="27" spans="1:19" s="1" customFormat="1" ht="24">
-      <c r="A27" s="32"/>
+    <row r="27" spans="1:19" ht="24">
+      <c r="A27" s="2"/>
       <c r="B27" s="36">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -7188,26 +7368,26 @@
       <c r="C27" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E27" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="G27" s="37" t="s">
+      <c r="D27" s="93" t="s">
+        <v>366</v>
+      </c>
+      <c r="E27" s="93" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="H27" s="37" t="s">
-        <v>129</v>
+      <c r="G27" s="93" t="s">
+        <v>368</v>
+      </c>
+      <c r="H27" s="93" t="s">
+        <v>369</v>
       </c>
       <c r="I27" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="37" t="s">
-        <v>130</v>
+      <c r="J27" s="93" t="s">
+        <v>370</v>
       </c>
       <c r="K27" s="37" t="s">
         <v>31</v>
@@ -7220,17 +7400,17 @@
         <v>20</v>
       </c>
       <c r="N27" s="37">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O27" s="43" t="s">
         <v>34</v>
       </c>
       <c r="P27" s="44">
-        <v>2.9100000000000001E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="Q27" s="44">
         <f t="shared" si="1"/>
-        <v>1.1640000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="R27" s="37"/>
       <c r="S27" s="37"/>
@@ -7245,25 +7425,25 @@
         <v>124</v>
       </c>
       <c r="D28" s="35" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E28" s="35" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F28" s="35" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I28" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J28" s="35" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K28" s="35" t="s">
         <v>31</v>
@@ -7301,25 +7481,25 @@
         <v>124</v>
       </c>
       <c r="D29" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>133</v>
+      </c>
+      <c r="G29" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="37" t="s">
         <v>136</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="G29" s="37" t="s">
-        <v>139</v>
-      </c>
-      <c r="H29" s="37" t="s">
-        <v>140</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>141</v>
       </c>
       <c r="K29" s="35" t="s">
         <v>31</v>
@@ -7357,25 +7537,25 @@
         <v>124</v>
       </c>
       <c r="D30" s="73" t="s">
+        <v>137</v>
+      </c>
+      <c r="E30" s="73" t="s">
+        <v>138</v>
+      </c>
+      <c r="F30" s="73" t="s">
+        <v>139</v>
+      </c>
+      <c r="G30" s="73" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" s="73" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="73" t="s">
         <v>142</v>
-      </c>
-      <c r="E30" s="73" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="73" t="s">
-        <v>144</v>
-      </c>
-      <c r="G30" s="73" t="s">
-        <v>145</v>
-      </c>
-      <c r="H30" s="73" t="s">
-        <v>146</v>
-      </c>
-      <c r="I30" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="73" t="s">
-        <v>147</v>
       </c>
       <c r="K30" s="73" t="s">
         <v>31</v>
@@ -7403,1518 +7583,1518 @@
       <c r="R30" s="73"/>
       <c r="S30" s="64"/>
     </row>
-    <row r="31" spans="1:19" s="1" customFormat="1" ht="24">
-      <c r="A31" s="32"/>
-      <c r="B31" s="36">
+    <row r="31" spans="1:19" ht="24">
+      <c r="A31" s="2"/>
+      <c r="B31" s="33">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="H31" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="I31" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="K31" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="37">
+      <c r="C31" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="D31" s="93" t="s">
+        <v>371</v>
+      </c>
+      <c r="E31" s="93" t="s">
+        <v>372</v>
+      </c>
+      <c r="F31" s="93" t="s">
+        <v>373</v>
+      </c>
+      <c r="G31" s="93" t="s">
+        <v>374</v>
+      </c>
+      <c r="H31" s="93" t="s">
+        <v>375</v>
+      </c>
+      <c r="I31" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="93" t="s">
+        <v>376</v>
+      </c>
+      <c r="K31" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="93">
         <v>1</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="73">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="35">
         <v>20</v>
       </c>
-      <c r="O31" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="P31" s="44">
+      <c r="O31" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P31" s="42">
+        <v>2.3699999999999999E-2</v>
+      </c>
+      <c r="Q31" s="42">
+        <f t="shared" si="1"/>
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="R31" s="35"/>
+      <c r="S31" s="64"/>
+    </row>
+    <row r="32" spans="1:19" s="1" customFormat="1" ht="24">
+      <c r="A32" s="32"/>
+      <c r="B32" s="36">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="H32" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="I32" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="K32" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L32" s="37">
+        <v>1</v>
+      </c>
+      <c r="M32" s="35">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N32" s="37">
+        <v>20</v>
+      </c>
+      <c r="O32" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="P32" s="44">
         <v>4.4299999999999999E-2</v>
       </c>
-      <c r="Q31" s="44">
+      <c r="Q32" s="44">
         <f t="shared" si="1"/>
         <v>0.88600000000000001</v>
       </c>
-      <c r="R31" s="37"/>
-      <c r="S31" s="37"/>
-    </row>
-    <row r="32" spans="1:19" s="1" customFormat="1">
-      <c r="A32" s="32"/>
-      <c r="B32" s="33">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="C32" s="34" t="s">
+      <c r="R32" s="37"/>
+      <c r="S32" s="37"/>
+    </row>
+    <row r="33" spans="1:19" s="1" customFormat="1">
+      <c r="A33" s="32"/>
+      <c r="B33" s="33">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="35" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="D32" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="F32" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="G32" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="K32" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L32" s="35">
+      <c r="K33" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="35">
         <v>2</v>
       </c>
-      <c r="M32" s="35">
+      <c r="M33" s="35">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="N32" s="35">
+      <c r="N33" s="35">
         <v>100</v>
       </c>
-      <c r="O32" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P32" s="42">
+      <c r="O33" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P33" s="42">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="Q32" s="42">
+      <c r="Q33" s="42">
         <f t="shared" si="1"/>
         <v>0.57999999999999996</v>
       </c>
-      <c r="R32" s="35"/>
-      <c r="S32" s="49"/>
-    </row>
-    <row r="33" spans="1:19" s="1" customFormat="1" ht="25.5">
-      <c r="A33" s="32"/>
-      <c r="B33" s="36">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C33" s="38" t="s">
-        <v>161</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="E33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="G33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="K33" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="L33" s="39">
+      <c r="R33" s="35"/>
+      <c r="S33" s="49"/>
+    </row>
+    <row r="34" spans="1:19" s="1" customFormat="1" ht="25.5">
+      <c r="A34" s="32"/>
+      <c r="B34" s="36">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="L34" s="39">
         <v>6</v>
       </c>
-      <c r="M33" s="35">
+      <c r="M34" s="35">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="N33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O33" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q33" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R33" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="S33" s="37"/>
-    </row>
-    <row r="34" spans="1:19" s="1" customFormat="1" ht="25.5">
-      <c r="A34" s="32"/>
-      <c r="B34" s="33">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="E34" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="F34" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="G34" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="H34" s="40" t="s">
-        <v>169</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="K34" s="40" t="s">
+      <c r="N34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q34" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R34" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="S34" s="37"/>
+    </row>
+    <row r="35" spans="1:19" s="1" customFormat="1" ht="25.5">
+      <c r="A35" s="32"/>
+      <c r="B35" s="33">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="D35" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="40" t="s">
         <v>164</v>
       </c>
-      <c r="L34" s="40">
+      <c r="G35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="40" t="s">
+        <v>159</v>
+      </c>
+      <c r="L35" s="40">
         <v>1</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M35" s="35">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N34" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="O34" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P34" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q34" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R34" s="50" t="s">
+      <c r="N35" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q35" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R35" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="S35" s="49"/>
+    </row>
+    <row r="36" spans="1:19" s="76" customFormat="1">
+      <c r="A36" s="69"/>
+      <c r="B36" s="70">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="80" t="s">
         <v>165</v>
       </c>
-      <c r="S34" s="49"/>
-    </row>
-    <row r="35" spans="1:19" s="76" customFormat="1">
-      <c r="A35" s="69"/>
-      <c r="B35" s="70">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="C35" s="80" t="s">
+      <c r="D36" s="72" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="72" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="G36" s="72" t="s">
+        <v>169</v>
+      </c>
+      <c r="H36" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="D35" s="72" t="s">
+      <c r="I36" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="72" t="s">
         <v>171</v>
       </c>
-      <c r="E35" s="72" t="s">
-        <v>172</v>
-      </c>
-      <c r="F35" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="72" t="s">
-        <v>174</v>
-      </c>
-      <c r="H35" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="I35" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J35" s="72" t="s">
-        <v>176</v>
-      </c>
-      <c r="K35" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" s="72">
+      <c r="K36" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="L36" s="72">
         <v>1</v>
       </c>
-      <c r="M35" s="73">
+      <c r="M36" s="73">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N35" s="72">
+      <c r="N36" s="72">
         <v>15</v>
       </c>
-      <c r="O35" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="P35" s="75">
+      <c r="O36" s="81" t="s">
+        <v>34</v>
+      </c>
+      <c r="P36" s="75">
         <v>0.2029</v>
       </c>
-      <c r="Q35" s="75">
-        <f t="shared" ref="Q35:Q42" si="3">P35*N35</f>
+      <c r="Q36" s="75">
+        <f t="shared" ref="Q36:Q43" si="3">P36*N36</f>
         <v>3.0434999999999999</v>
       </c>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
-    </row>
-    <row r="36" spans="1:19" s="1" customFormat="1" ht="24">
-      <c r="A36" s="32"/>
-      <c r="B36" s="33">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="C36" s="34" t="s">
+      <c r="R36" s="72"/>
+      <c r="S36" s="72"/>
+    </row>
+    <row r="37" spans="1:19" s="1" customFormat="1" ht="24">
+      <c r="A37" s="32"/>
+      <c r="B37" s="33">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D37" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H37" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="I37" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="D36" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G36" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="H36" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="K36" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L36" s="35">
+      <c r="K37" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="35">
         <v>1</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M37" s="35">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N37" s="35">
         <v>15</v>
       </c>
-      <c r="O36" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="P36" s="42">
+      <c r="O37" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="P37" s="42">
         <v>0.13009999999999999</v>
       </c>
-      <c r="Q36" s="42">
+      <c r="Q37" s="42">
         <f t="shared" si="3"/>
         <v>1.9514999999999998</v>
       </c>
-      <c r="R36" s="35"/>
-      <c r="S36" s="49"/>
-    </row>
-    <row r="37" spans="1:19" s="76" customFormat="1">
-      <c r="A37" s="69"/>
-      <c r="B37" s="70">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C37" s="80" t="s">
-        <v>183</v>
-      </c>
-      <c r="D37" s="72" t="s">
-        <v>184</v>
-      </c>
-      <c r="E37" s="72" t="s">
-        <v>185</v>
-      </c>
-      <c r="F37" s="72" t="s">
-        <v>186</v>
-      </c>
-      <c r="G37" s="72">
-        <v>8266292</v>
-      </c>
-      <c r="H37" s="72" t="s">
-        <v>187</v>
-      </c>
-      <c r="I37" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" s="72" t="s">
-        <v>188</v>
-      </c>
-      <c r="K37" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="L37" s="72">
-        <v>1</v>
-      </c>
-      <c r="M37" s="73">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N37" s="72">
-        <v>11</v>
-      </c>
-      <c r="O37" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="P37" s="75">
-        <v>0.25319999999999998</v>
-      </c>
-      <c r="Q37" s="75">
-        <f t="shared" si="3"/>
-        <v>2.7851999999999997</v>
-      </c>
-      <c r="R37" s="72"/>
-      <c r="S37" s="72"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="49"/>
     </row>
     <row r="38" spans="1:19" s="76" customFormat="1">
       <c r="A38" s="69"/>
-      <c r="B38" s="77">
+      <c r="B38" s="70">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="71" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" s="73" t="s">
-        <v>190</v>
-      </c>
-      <c r="E38" s="73" t="s">
-        <v>191</v>
-      </c>
-      <c r="F38" s="73" t="s">
-        <v>192</v>
-      </c>
-      <c r="G38" s="73" t="s">
-        <v>193</v>
-      </c>
-      <c r="H38" s="73" t="s">
-        <v>59</v>
+      <c r="C38" s="80" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" s="72" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="F38" s="72" t="s">
+        <v>181</v>
+      </c>
+      <c r="G38" s="72">
+        <v>8266292</v>
+      </c>
+      <c r="H38" s="72" t="s">
+        <v>182</v>
       </c>
       <c r="I38" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="J38" s="73" t="s">
-        <v>194</v>
-      </c>
-      <c r="K38" s="73" t="s">
-        <v>195</v>
-      </c>
-      <c r="L38" s="73">
+      <c r="J38" s="72" t="s">
+        <v>183</v>
+      </c>
+      <c r="K38" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="L38" s="72">
         <v>1</v>
       </c>
       <c r="M38" s="73">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N38" s="73">
-        <v>15</v>
-      </c>
-      <c r="O38" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="P38" s="79">
-        <v>0.2006</v>
-      </c>
-      <c r="Q38" s="79">
+      <c r="N38" s="72">
+        <v>11</v>
+      </c>
+      <c r="O38" s="81" t="s">
+        <v>34</v>
+      </c>
+      <c r="P38" s="75">
+        <v>0.25319999999999998</v>
+      </c>
+      <c r="Q38" s="75">
         <f t="shared" si="3"/>
-        <v>3.0089999999999999</v>
-      </c>
-      <c r="R38" s="73"/>
-      <c r="S38" s="64"/>
+        <v>2.7851999999999997</v>
+      </c>
+      <c r="R38" s="72"/>
+      <c r="S38" s="72"/>
     </row>
     <row r="39" spans="1:19" s="76" customFormat="1">
       <c r="A39" s="69"/>
-      <c r="B39" s="70">
+      <c r="B39" s="77">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="80" t="s">
+      <c r="C39" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="D39" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="73" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="73" t="s">
         <v>189</v>
       </c>
-      <c r="D39" s="72" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="F39" s="72" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" s="72" t="s">
-        <v>198</v>
-      </c>
-      <c r="H39" s="72" t="s">
-        <v>199</v>
-      </c>
-      <c r="I39" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="72" t="s">
-        <v>200</v>
-      </c>
-      <c r="K39" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="L39" s="72">
+      <c r="K39" s="73" t="s">
+        <v>190</v>
+      </c>
+      <c r="L39" s="73">
         <v>1</v>
       </c>
       <c r="M39" s="73">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N39" s="72">
+      <c r="N39" s="73">
+        <v>15</v>
+      </c>
+      <c r="O39" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="P39" s="79">
+        <v>0.2006</v>
+      </c>
+      <c r="Q39" s="79">
+        <f t="shared" si="3"/>
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="R39" s="73"/>
+      <c r="S39" s="64"/>
+    </row>
+    <row r="40" spans="1:19" s="76" customFormat="1">
+      <c r="A40" s="69"/>
+      <c r="B40" s="70">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" s="72" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="H40" s="72" t="s">
+        <v>194</v>
+      </c>
+      <c r="I40" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="K40" s="72" t="s">
+        <v>196</v>
+      </c>
+      <c r="L40" s="72">
+        <v>1</v>
+      </c>
+      <c r="M40" s="73">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N40" s="72">
         <v>20</v>
       </c>
-      <c r="O39" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="P39" s="75">
+      <c r="O40" s="81" t="s">
+        <v>34</v>
+      </c>
+      <c r="P40" s="75">
         <v>6.6799999999999998E-2</v>
       </c>
-      <c r="Q39" s="75">
+      <c r="Q40" s="75">
         <f t="shared" si="3"/>
         <v>1.3359999999999999</v>
       </c>
-      <c r="R39" s="72"/>
-      <c r="S39" s="72"/>
-    </row>
-    <row r="40" spans="1:19" s="1" customFormat="1" ht="36">
-      <c r="A40" s="32"/>
-      <c r="B40" s="33">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="D40" s="35" t="s">
+      <c r="R40" s="72"/>
+      <c r="S40" s="72"/>
+    </row>
+    <row r="41" spans="1:19" s="1" customFormat="1" ht="36">
+      <c r="A41" s="32"/>
+      <c r="B41" s="33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>198</v>
+      </c>
+      <c r="F41" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="I41" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="K41" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="E40" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="G40" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="H40" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="K40" s="35" t="s">
-        <v>207</v>
-      </c>
-      <c r="L40" s="35">
-        <v>1</v>
-      </c>
-      <c r="M40" s="35">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="N40" s="35">
-        <v>15</v>
-      </c>
-      <c r="O40" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="P40" s="42">
-        <v>0.1326</v>
-      </c>
-      <c r="Q40" s="42">
-        <f t="shared" si="3"/>
-        <v>1.9889999999999999</v>
-      </c>
-      <c r="R40" s="35"/>
-      <c r="S40" s="49"/>
-    </row>
-    <row r="41" spans="1:19" s="1" customFormat="1" ht="24">
-      <c r="A41" s="32"/>
-      <c r="B41" s="36">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="D41" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="H41" s="37" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="K41" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L41" s="37">
+      <c r="L41" s="35">
         <v>1</v>
       </c>
       <c r="M41" s="35">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N41" s="37">
-        <v>20</v>
-      </c>
-      <c r="O41" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="P41" s="44">
-        <v>2.0799999999999999E-2</v>
-      </c>
-      <c r="Q41" s="44">
+      <c r="N41" s="35">
+        <v>15</v>
+      </c>
+      <c r="O41" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="P41" s="42">
+        <v>0.1326</v>
+      </c>
+      <c r="Q41" s="42">
         <f t="shared" si="3"/>
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-    </row>
-    <row r="42" spans="1:19" s="1" customFormat="1" ht="48">
+        <v>1.9889999999999999</v>
+      </c>
+      <c r="R41" s="35"/>
+      <c r="S41" s="49"/>
+    </row>
+    <row r="42" spans="1:19" s="1" customFormat="1" ht="24">
       <c r="A42" s="32"/>
-      <c r="B42" s="33">
+      <c r="B42" s="36">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="C42" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H42" s="37" t="s">
         <v>208</v>
       </c>
-      <c r="D42" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="E42" s="35" t="s">
-        <v>216</v>
-      </c>
-      <c r="F42" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="G42" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="H42" s="35" t="s">
-        <v>219</v>
-      </c>
       <c r="I42" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J42" s="35" t="s">
-        <v>220</v>
+      <c r="J42" s="37" t="s">
+        <v>209</v>
       </c>
       <c r="K42" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="L42" s="35">
+      <c r="L42" s="37">
         <v>1</v>
       </c>
       <c r="M42" s="35">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="N42" s="35">
+      <c r="N42" s="37">
+        <v>20</v>
+      </c>
+      <c r="O42" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="P42" s="44">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="Q42" s="44">
+        <f t="shared" si="3"/>
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="R42" s="37"/>
+      <c r="S42" s="37"/>
+    </row>
+    <row r="43" spans="1:19" s="1" customFormat="1" ht="48">
+      <c r="A43" s="32"/>
+      <c r="B43" s="33">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C43" s="38" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="I43" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="K43" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L43" s="35">
+        <v>1</v>
+      </c>
+      <c r="M43" s="35">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="N43" s="35">
         <v>100</v>
       </c>
-      <c r="O42" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P42" s="42">
+      <c r="O43" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P43" s="42">
         <v>6.7999999999999996E-3</v>
       </c>
-      <c r="Q42" s="42">
+      <c r="Q43" s="42">
         <f t="shared" si="3"/>
         <v>0.67999999999999994</v>
       </c>
-      <c r="R42" s="35"/>
-      <c r="S42" s="49"/>
-    </row>
-    <row r="43" spans="1:19" s="1" customFormat="1" ht="24">
-      <c r="A43" s="32"/>
-      <c r="B43" s="36">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="C43" s="38" t="s">
+      <c r="R43" s="35"/>
+      <c r="S43" s="49"/>
+    </row>
+    <row r="44" spans="1:19" s="1" customFormat="1" ht="24">
+      <c r="A44" s="32"/>
+      <c r="B44" s="36">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="D44" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>218</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="L44" s="39">
+        <v>1</v>
+      </c>
+      <c r="M44" s="35">
+        <f t="shared" ref="M44:M71" si="4">L44*10</f>
+        <v>10</v>
+      </c>
+      <c r="N44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q44" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="R44" s="39"/>
+      <c r="S44" s="37"/>
+    </row>
+    <row r="45" spans="1:19" s="1" customFormat="1" ht="36">
+      <c r="A45" s="32"/>
+      <c r="B45" s="33">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="D45" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="D43" s="39" t="s">
+      <c r="F45" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="E43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="39" t="s">
+      <c r="G45" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="G43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="K43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" s="39">
-        <v>1</v>
-      </c>
-      <c r="M43" s="35">
-        <f t="shared" ref="M43:M69" si="4">L43*10</f>
-        <v>10</v>
-      </c>
-      <c r="N43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" s="39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P43" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q43" s="47" t="s">
-        <v>31</v>
-      </c>
-      <c r="R43" s="39"/>
-      <c r="S43" s="37"/>
-    </row>
-    <row r="44" spans="1:19" s="1" customFormat="1" ht="36">
-      <c r="A44" s="32"/>
-      <c r="B44" s="33">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="C44" s="34" t="s">
+      <c r="H45" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="I45" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="E44" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="F44" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="G44" s="35" t="s">
-        <v>228</v>
-      </c>
-      <c r="H44" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="I44" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J44" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="K44" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L44" s="35">
-        <v>1</v>
-      </c>
-      <c r="M44" s="35">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="N44" s="35">
-        <v>20</v>
-      </c>
-      <c r="O44" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P44" s="42">
-        <v>3.04E-2</v>
-      </c>
-      <c r="Q44" s="42">
-        <f t="shared" ref="Q44:Q68" si="5">P44*N44</f>
-        <v>0.60799999999999998</v>
-      </c>
-      <c r="R44" s="35"/>
-      <c r="S44" s="49"/>
-    </row>
-    <row r="45" spans="1:19" s="1" customFormat="1" ht="48">
-      <c r="A45" s="32"/>
-      <c r="B45" s="36">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>231</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>232</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>235</v>
-      </c>
-      <c r="I45" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="37" t="s">
-        <v>236</v>
-      </c>
       <c r="K45" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="L45" s="37">
+      <c r="L45" s="35">
         <v>1</v>
       </c>
       <c r="M45" s="35">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N45" s="37">
+      <c r="N45" s="35">
         <v>20</v>
       </c>
-      <c r="O45" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P45" s="44">
+      <c r="O45" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P45" s="42">
+        <v>3.04E-2</v>
+      </c>
+      <c r="Q45" s="42">
+        <f t="shared" ref="Q45:Q70" si="5">P45*N45</f>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="R45" s="35"/>
+      <c r="S45" s="49"/>
+    </row>
+    <row r="46" spans="1:19" s="1" customFormat="1" ht="48">
+      <c r="A46" s="32"/>
+      <c r="B46" s="36">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="K46" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="L46" s="37">
+        <v>1</v>
+      </c>
+      <c r="M46" s="35">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N46" s="37">
+        <v>20</v>
+      </c>
+      <c r="O46" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P46" s="44">
         <v>3.3500000000000002E-2</v>
       </c>
-      <c r="Q45" s="44">
+      <c r="Q46" s="44">
         <f t="shared" si="5"/>
         <v>0.67</v>
       </c>
-      <c r="R45" s="37"/>
-      <c r="S45" s="37"/>
-    </row>
-    <row r="46" spans="1:19" s="1" customFormat="1">
-      <c r="A46" s="32"/>
-      <c r="B46" s="33">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="C46" s="38" t="s">
+      <c r="R46" s="37"/>
+      <c r="S46" s="37"/>
+    </row>
+    <row r="47" spans="1:19" s="1" customFormat="1">
+      <c r="A47" s="32"/>
+      <c r="B47" s="33">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="G47" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="H47" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="D46" s="35" t="s">
+      <c r="K47" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="E46" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="F46" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="G46" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="H46" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="K46" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="L46" s="35">
+      <c r="L47" s="35">
         <v>2</v>
       </c>
-      <c r="M46" s="35">
+      <c r="M47" s="35">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N46" s="35">
+      <c r="N47" s="35">
         <v>100</v>
       </c>
-      <c r="O46" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P46" s="42">
+      <c r="O47" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P47" s="42">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="Q46" s="42">
+      <c r="Q47" s="42">
         <f t="shared" si="5"/>
         <v>0.08</v>
       </c>
-      <c r="R46" s="35"/>
-      <c r="S46" s="49"/>
-    </row>
-    <row r="47" spans="1:19" s="76" customFormat="1">
-      <c r="A47" s="69"/>
-      <c r="B47" s="70">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="C47" s="80" t="s">
-        <v>237</v>
-      </c>
-      <c r="D47" s="72" t="s">
+      <c r="R47" s="35"/>
+      <c r="S47" s="49"/>
+    </row>
+    <row r="48" spans="1:19" s="76" customFormat="1">
+      <c r="A48" s="69"/>
+      <c r="B48" s="70">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" s="72" t="s">
+        <v>239</v>
+      </c>
+      <c r="E48" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="F48" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="G48" s="72" t="s">
+        <v>242</v>
+      </c>
+      <c r="H48" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="I48" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="K48" s="72" t="s">
         <v>244</v>
       </c>
-      <c r="E47" s="72" t="s">
-        <v>245</v>
-      </c>
-      <c r="F47" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="G47" s="72" t="s">
-        <v>247</v>
-      </c>
-      <c r="H47" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="72" t="s">
-        <v>248</v>
-      </c>
-      <c r="K47" s="72" t="s">
-        <v>249</v>
-      </c>
-      <c r="L47" s="72">
+      <c r="L48" s="72">
         <v>2</v>
       </c>
-      <c r="M47" s="73">
+      <c r="M48" s="73">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N47" s="72">
+      <c r="N48" s="72">
         <v>40</v>
       </c>
-      <c r="O47" s="81" t="s">
-        <v>34</v>
-      </c>
-      <c r="P47" s="75">
+      <c r="O48" s="81" t="s">
+        <v>34</v>
+      </c>
+      <c r="P48" s="75">
         <v>2.1700000000000001E-2</v>
       </c>
-      <c r="Q47" s="75">
+      <c r="Q48" s="75">
         <f t="shared" si="5"/>
         <v>0.86799999999999999</v>
       </c>
-      <c r="R47" s="72"/>
-      <c r="S47" s="72"/>
-    </row>
-    <row r="48" spans="1:19" s="76" customFormat="1">
-      <c r="A48" s="69"/>
-      <c r="B48" s="77">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="C48" s="80" t="s">
-        <v>237</v>
-      </c>
-      <c r="D48" s="73" t="s">
+      <c r="R48" s="72"/>
+      <c r="S48" s="72"/>
+    </row>
+    <row r="49" spans="1:19" s="76" customFormat="1">
+      <c r="A49" s="69"/>
+      <c r="B49" s="77">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="C49" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="E49" s="73" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" s="73" t="s">
+        <v>247</v>
+      </c>
+      <c r="G49" s="73" t="s">
+        <v>248</v>
+      </c>
+      <c r="H49" s="73" t="s">
+        <v>30</v>
+      </c>
+      <c r="I49" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="73" t="s">
+        <v>249</v>
+      </c>
+      <c r="K49" s="73" t="s">
         <v>250</v>
       </c>
-      <c r="E48" s="73" t="s">
-        <v>251</v>
-      </c>
-      <c r="F48" s="73" t="s">
-        <v>252</v>
-      </c>
-      <c r="G48" s="73" t="s">
-        <v>253</v>
-      </c>
-      <c r="H48" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="73" t="s">
-        <v>254</v>
-      </c>
-      <c r="K48" s="73" t="s">
-        <v>255</v>
-      </c>
-      <c r="L48" s="73">
+      <c r="L49" s="73">
         <v>5</v>
       </c>
-      <c r="M48" s="73">
+      <c r="M49" s="73">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="N48" s="73">
+      <c r="N49" s="73">
         <v>60</v>
       </c>
-      <c r="O48" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="P48" s="79">
+      <c r="O49" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="P49" s="79">
         <v>1.41E-2</v>
       </c>
-      <c r="Q48" s="79">
+      <c r="Q49" s="79">
         <f t="shared" si="5"/>
         <v>0.84599999999999997</v>
       </c>
-      <c r="R48" s="73"/>
-      <c r="S48" s="64"/>
-    </row>
-    <row r="49" spans="1:19" s="1" customFormat="1">
-      <c r="A49" s="32"/>
-      <c r="B49" s="36">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="C49" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D49" s="37" t="s">
-        <v>256</v>
-      </c>
-      <c r="E49" s="37" t="s">
-        <v>257</v>
-      </c>
-      <c r="F49" s="37" t="s">
+      <c r="R49" s="73"/>
+      <c r="S49" s="64"/>
+    </row>
+    <row r="50" spans="1:19" s="1" customFormat="1">
+      <c r="A50" s="32"/>
+      <c r="B50" s="36">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="C50" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="E50" s="37" t="s">
         <v>252</v>
       </c>
-      <c r="G49" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="H49" s="37" t="s">
+      <c r="F50" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="H50" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="I49" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="K49" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="L49" s="37">
+      <c r="I50" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="K50" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="L50" s="37">
         <v>2</v>
       </c>
-      <c r="M49" s="35">
+      <c r="M50" s="35">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="N49" s="37">
+      <c r="N50" s="37">
         <v>100</v>
       </c>
-      <c r="O49" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="P49" s="44">
+      <c r="O50" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="P50" s="44">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q49" s="44">
+      <c r="Q50" s="44">
         <f t="shared" si="5"/>
         <v>0.06</v>
       </c>
-      <c r="R49" s="37"/>
-      <c r="S49" s="37"/>
-    </row>
-    <row r="50" spans="1:19" s="1" customFormat="1">
-      <c r="A50" s="32"/>
-      <c r="B50" s="33">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D50" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="F50" s="35" t="s">
-        <v>246</v>
-      </c>
-      <c r="G50" s="35" t="s">
-        <v>263</v>
-      </c>
-      <c r="H50" s="35" t="s">
+      <c r="R50" s="37"/>
+      <c r="S50" s="37"/>
+    </row>
+    <row r="51" spans="1:19" s="1" customFormat="1">
+      <c r="A51" s="32"/>
+      <c r="B51" s="33">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D51" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="F51" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="G51" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="H51" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="I50" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J50" s="35" t="s">
-        <v>264</v>
-      </c>
-      <c r="K50" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="L50" s="35">
+      <c r="I51" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="K51" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="L51" s="35">
         <v>1</v>
       </c>
-      <c r="M50" s="35">
+      <c r="M51" s="35">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N50" s="35">
+      <c r="N51" s="35">
         <v>100</v>
       </c>
-      <c r="O50" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P50" s="42">
+      <c r="O51" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P51" s="42">
         <v>1E-3</v>
       </c>
-      <c r="Q50" s="42">
+      <c r="Q51" s="42">
         <f t="shared" si="5"/>
         <v>0.1</v>
       </c>
-      <c r="R50" s="35"/>
-      <c r="S50" s="49"/>
-    </row>
-    <row r="51" spans="1:19" s="76" customFormat="1">
-      <c r="A51" s="69"/>
-      <c r="B51" s="70">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="C51" s="80" t="s">
-        <v>237</v>
-      </c>
-      <c r="D51" s="72" t="s">
-        <v>266</v>
-      </c>
-      <c r="E51" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="F51" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="G51" s="72" t="s">
-        <v>268</v>
-      </c>
-      <c r="H51" s="72" t="s">
+      <c r="R51" s="35"/>
+      <c r="S51" s="49"/>
+    </row>
+    <row r="52" spans="1:19" s="76" customFormat="1">
+      <c r="A52" s="69"/>
+      <c r="B52" s="70">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="C52" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" s="72" t="s">
+        <v>261</v>
+      </c>
+      <c r="E52" s="72" t="s">
+        <v>262</v>
+      </c>
+      <c r="F52" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="72" t="s">
+        <v>263</v>
+      </c>
+      <c r="H52" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="I51" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J51" s="72" t="s">
-        <v>269</v>
-      </c>
-      <c r="K51" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="L51" s="72">
+      <c r="I52" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="K52" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="L52" s="72">
         <v>3</v>
       </c>
-      <c r="M51" s="73">
+      <c r="M52" s="73">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="N51" s="72">
+      <c r="N52" s="72">
         <v>100</v>
       </c>
-      <c r="O51" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="P51" s="75">
+      <c r="O52" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="P52" s="75">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q51" s="75">
+      <c r="Q52" s="75">
         <f t="shared" si="5"/>
         <v>0.11</v>
       </c>
-      <c r="R51" s="72"/>
-      <c r="S51" s="72"/>
-    </row>
-    <row r="52" spans="1:19" s="1" customFormat="1" ht="36">
-      <c r="A52" s="32"/>
-      <c r="B52" s="33">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D52" s="35" t="s">
+      <c r="R52" s="72"/>
+      <c r="S52" s="72"/>
+    </row>
+    <row r="53" spans="1:19" s="1" customFormat="1" ht="36">
+      <c r="A53" s="32"/>
+      <c r="B53" s="33">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="F53" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="G53" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="H53" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="I53" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="E52" s="35" t="s">
+      <c r="K53" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="F52" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="G52" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="H52" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="K52" s="35" t="s">
-        <v>277</v>
-      </c>
-      <c r="L52" s="35">
+      <c r="L53" s="35">
         <v>3</v>
       </c>
-      <c r="M52" s="35">
+      <c r="M53" s="35">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="N52" s="35">
+      <c r="N53" s="35">
         <v>100</v>
       </c>
-      <c r="O52" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P52" s="42">
+      <c r="O53" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P53" s="42">
         <v>4.4999999999999997E-3</v>
       </c>
-      <c r="Q52" s="42">
+      <c r="Q53" s="42">
         <f t="shared" si="5"/>
         <v>0.44999999999999996</v>
       </c>
-      <c r="R52" s="35"/>
-      <c r="S52" s="49"/>
-    </row>
-    <row r="53" spans="1:19" s="1" customFormat="1">
-      <c r="A53" s="32"/>
-      <c r="B53" s="36">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>278</v>
-      </c>
-      <c r="E53" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="F53" s="37" t="s">
-        <v>246</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>280</v>
-      </c>
-      <c r="H53" s="37" t="s">
+      <c r="R53" s="35"/>
+      <c r="S53" s="49"/>
+    </row>
+    <row r="54" spans="1:19" s="1" customFormat="1">
+      <c r="A54" s="32"/>
+      <c r="B54" s="36">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>273</v>
+      </c>
+      <c r="E54" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="F54" s="37" t="s">
+        <v>241</v>
+      </c>
+      <c r="G54" s="37" t="s">
+        <v>275</v>
+      </c>
+      <c r="H54" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="I53" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J53" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="K53" s="37" t="s">
-        <v>282</v>
-      </c>
-      <c r="L53" s="37">
+      <c r="I54" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J54" s="37" t="s">
+        <v>276</v>
+      </c>
+      <c r="K54" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="L54" s="37">
         <v>1</v>
       </c>
-      <c r="M53" s="35">
+      <c r="M54" s="35">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N53" s="37">
+      <c r="N54" s="37">
         <v>100</v>
       </c>
-      <c r="O53" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="P53" s="44">
+      <c r="O54" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="P54" s="44">
         <v>1.1999999999999999E-3</v>
       </c>
-      <c r="Q53" s="44">
+      <c r="Q54" s="44">
         <f t="shared" si="5"/>
         <v>0.12</v>
       </c>
-      <c r="R53" s="37"/>
-      <c r="S53" s="37"/>
-    </row>
-    <row r="54" spans="1:19" s="76" customFormat="1">
-      <c r="A54" s="69"/>
-      <c r="B54" s="77">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="C54" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="D54" s="73" t="s">
-        <v>283</v>
-      </c>
-      <c r="E54" s="73" t="s">
-        <v>284</v>
-      </c>
-      <c r="F54" s="73" t="s">
-        <v>246</v>
-      </c>
-      <c r="G54" s="73" t="s">
-        <v>285</v>
-      </c>
-      <c r="H54" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="I54" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J54" s="73" t="s">
-        <v>286</v>
-      </c>
-      <c r="K54" s="73" t="s">
-        <v>287</v>
-      </c>
-      <c r="L54" s="73">
-        <v>1</v>
-      </c>
-      <c r="M54" s="73">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="N54" s="73">
-        <v>100</v>
-      </c>
-      <c r="O54" s="82" t="s">
-        <v>34</v>
-      </c>
-      <c r="P54" s="79">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="Q54" s="79">
-        <f t="shared" si="5"/>
-        <v>0.21</v>
-      </c>
-      <c r="R54" s="73"/>
-      <c r="S54" s="64"/>
+      <c r="R54" s="37"/>
+      <c r="S54" s="37"/>
     </row>
     <row r="55" spans="1:19" s="76" customFormat="1">
       <c r="A55" s="69"/>
-      <c r="B55" s="70">
+      <c r="B55" s="77">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C55" s="71" t="s">
-        <v>237</v>
-      </c>
-      <c r="D55" s="72" t="s">
-        <v>288</v>
-      </c>
-      <c r="E55" s="72" t="s">
-        <v>289</v>
-      </c>
-      <c r="F55" s="72" t="s">
-        <v>246</v>
-      </c>
-      <c r="G55" s="72" t="s">
-        <v>290</v>
-      </c>
-      <c r="H55" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="73" t="s">
+        <v>278</v>
+      </c>
+      <c r="E55" s="73" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="G55" s="73" t="s">
+        <v>280</v>
+      </c>
+      <c r="H55" s="73" t="s">
         <v>30</v>
       </c>
       <c r="I55" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="J55" s="72" t="s">
-        <v>291</v>
-      </c>
-      <c r="K55" s="72" t="s">
-        <v>292</v>
-      </c>
-      <c r="L55" s="72">
+      <c r="J55" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="K55" s="73" t="s">
+        <v>282</v>
+      </c>
+      <c r="L55" s="73">
         <v>1</v>
       </c>
       <c r="M55" s="73">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N55" s="72">
+      <c r="N55" s="73">
+        <v>100</v>
+      </c>
+      <c r="O55" s="82" t="s">
+        <v>34</v>
+      </c>
+      <c r="P55" s="79">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="Q55" s="79">
+        <f t="shared" si="5"/>
+        <v>0.21</v>
+      </c>
+      <c r="R55" s="73"/>
+      <c r="S55" s="64"/>
+    </row>
+    <row r="56" spans="1:19" s="76" customFormat="1">
+      <c r="A56" s="69"/>
+      <c r="B56" s="70">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="C56" s="71" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="E56" s="72" t="s">
+        <v>284</v>
+      </c>
+      <c r="F56" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="G56" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="H56" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="I56" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J56" s="72" t="s">
+        <v>286</v>
+      </c>
+      <c r="K56" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="L56" s="72">
+        <v>1</v>
+      </c>
+      <c r="M56" s="73">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N56" s="72">
         <v>20</v>
       </c>
-      <c r="O55" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="P55" s="75">
+      <c r="O56" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="P56" s="75">
         <v>3.7499999999999999E-2</v>
       </c>
-      <c r="Q55" s="75">
+      <c r="Q56" s="75">
         <f t="shared" si="5"/>
         <v>0.75</v>
       </c>
-      <c r="R55" s="72"/>
-      <c r="S55" s="72"/>
-    </row>
-    <row r="56" spans="1:19" s="76" customFormat="1">
-      <c r="A56" s="69"/>
-      <c r="B56" s="77">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="C56" s="71" t="s">
-        <v>293</v>
-      </c>
-      <c r="D56" s="73" t="s">
-        <v>294</v>
-      </c>
-      <c r="E56" s="73" t="s">
-        <v>295</v>
-      </c>
-      <c r="F56" s="73" t="s">
-        <v>296</v>
-      </c>
-      <c r="G56" s="73" t="s">
-        <v>296</v>
-      </c>
-      <c r="H56" s="73" t="s">
-        <v>297</v>
-      </c>
-      <c r="I56" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J56" s="73" t="s">
-        <v>298</v>
-      </c>
-      <c r="K56" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" s="73">
-        <v>2</v>
-      </c>
-      <c r="M56" s="73">
-        <f t="shared" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="N56" s="73">
-        <v>25</v>
-      </c>
-      <c r="O56" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="P56" s="79">
-        <v>0.1729</v>
-      </c>
-      <c r="Q56" s="79">
-        <f t="shared" si="5"/>
-        <v>4.3224999999999998</v>
-      </c>
-      <c r="R56" s="73"/>
-      <c r="S56" s="64"/>
-    </row>
-    <row r="57" spans="1:19" s="1" customFormat="1">
-      <c r="A57" s="32"/>
+      <c r="R56" s="72"/>
+      <c r="S56" s="72"/>
+    </row>
+    <row r="57" spans="1:19">
+      <c r="A57" s="2"/>
       <c r="B57" s="36">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="D57" s="37" t="s">
-        <v>300</v>
-      </c>
-      <c r="E57" s="37" t="s">
-        <v>301</v>
-      </c>
-      <c r="F57" s="37" t="s">
-        <v>302</v>
-      </c>
-      <c r="G57" s="37" t="s">
-        <v>303</v>
-      </c>
-      <c r="H57" s="37" t="s">
-        <v>304</v>
-      </c>
-      <c r="I57" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="K57" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L57" s="37">
+      <c r="C57" s="94" t="s">
+        <v>232</v>
+      </c>
+      <c r="D57" s="93" t="s">
+        <v>377</v>
+      </c>
+      <c r="E57" s="93" t="s">
+        <v>378</v>
+      </c>
+      <c r="F57" s="93" t="s">
+        <v>241</v>
+      </c>
+      <c r="G57" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="H57" s="93" t="s">
+        <v>30</v>
+      </c>
+      <c r="I57" s="93" t="s">
+        <v>381</v>
+      </c>
+      <c r="J57" s="93" t="s">
+        <v>382</v>
+      </c>
+      <c r="K57" s="93" t="s">
+        <v>380</v>
+      </c>
+      <c r="L57" s="35">
         <v>1</v>
       </c>
-      <c r="M57" s="35">
+      <c r="M57" s="73">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N57" s="37">
-        <v>11</v>
-      </c>
-      <c r="O57" s="43" t="s">
-        <v>316</v>
-      </c>
-      <c r="P57" s="44">
-        <v>16.25</v>
+      <c r="N57" s="35">
+        <v>100</v>
+      </c>
+      <c r="O57" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="P57" s="42">
+        <v>1E-3</v>
       </c>
       <c r="Q57" s="44">
         <f t="shared" si="5"/>
-        <v>178.75</v>
-      </c>
-      <c r="R57" s="37"/>
-      <c r="S57" s="37"/>
+        <v>0.1</v>
+      </c>
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
     </row>
     <row r="58" spans="1:19" s="76" customFormat="1">
       <c r="A58" s="69"/>
@@ -8923,51 +9103,51 @@
         <v>49</v>
       </c>
       <c r="C58" s="71" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D58" s="73" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="E58" s="73" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="F58" s="73" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="G58" s="73" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="H58" s="73" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="I58" s="72" t="s">
         <v>31</v>
       </c>
       <c r="J58" s="73" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="K58" s="73" t="s">
         <v>31</v>
       </c>
       <c r="L58" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58" s="73">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N58" s="73">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="O58" s="78" t="s">
         <v>34</v>
       </c>
       <c r="P58" s="79">
-        <v>0.66659999999999997</v>
+        <v>0.1729</v>
       </c>
       <c r="Q58" s="79">
         <f t="shared" si="5"/>
-        <v>7.3325999999999993</v>
+        <v>4.3224999999999998</v>
       </c>
       <c r="R58" s="73"/>
       <c r="S58" s="64"/>
@@ -8979,22 +9159,22 @@
         <v>50</v>
       </c>
       <c r="C59" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D59" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="E59" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="F59" s="37" t="s">
+        <v>297</v>
+      </c>
+      <c r="G59" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="H59" s="37" t="s">
         <v>299</v>
-      </c>
-      <c r="D59" s="37" t="s">
-        <v>311</v>
-      </c>
-      <c r="E59" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="F59" s="37" t="s">
-        <v>313</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>314</v>
-      </c>
-      <c r="H59" s="37" t="s">
-        <v>315</v>
       </c>
       <c r="I59" s="37" t="s">
         <v>31</v>
@@ -9016,73 +9196,73 @@
         <v>11</v>
       </c>
       <c r="O59" s="43" t="s">
-        <v>373</v>
+        <v>311</v>
       </c>
       <c r="P59" s="44">
-        <v>6.25</v>
+        <v>16.25</v>
       </c>
       <c r="Q59" s="44">
         <f t="shared" si="5"/>
-        <v>68.75</v>
+        <v>178.75</v>
       </c>
       <c r="R59" s="37"/>
       <c r="S59" s="37"/>
     </row>
-    <row r="60" spans="1:19" s="1" customFormat="1">
-      <c r="A60" s="32"/>
-      <c r="B60" s="33">
+    <row r="60" spans="1:19" s="76" customFormat="1">
+      <c r="A60" s="69"/>
+      <c r="B60" s="77">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="C60" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="D60" s="35" t="s">
-        <v>317</v>
-      </c>
-      <c r="E60" s="35" t="s">
-        <v>318</v>
-      </c>
-      <c r="F60" s="35" t="s">
-        <v>319</v>
-      </c>
-      <c r="G60" s="35" t="s">
-        <v>320</v>
-      </c>
-      <c r="H60" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="I60" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J60" s="35" t="s">
-        <v>322</v>
-      </c>
-      <c r="K60" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L60" s="35">
+      <c r="C60" s="71" t="s">
+        <v>294</v>
+      </c>
+      <c r="D60" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="E60" s="73" t="s">
+        <v>301</v>
+      </c>
+      <c r="F60" s="73" t="s">
+        <v>302</v>
+      </c>
+      <c r="G60" s="73" t="s">
+        <v>303</v>
+      </c>
+      <c r="H60" s="73" t="s">
+        <v>304</v>
+      </c>
+      <c r="I60" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J60" s="73" t="s">
+        <v>305</v>
+      </c>
+      <c r="K60" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="L60" s="73">
         <v>1</v>
       </c>
-      <c r="M60" s="35">
+      <c r="M60" s="73">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N60" s="35">
+      <c r="N60" s="73">
         <v>11</v>
       </c>
-      <c r="O60" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="P60" s="42">
-        <v>0.26750000000000002</v>
-      </c>
-      <c r="Q60" s="42">
+      <c r="O60" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="P60" s="79">
+        <v>0.66659999999999997</v>
+      </c>
+      <c r="Q60" s="79">
         <f t="shared" si="5"/>
-        <v>2.9425000000000003</v>
-      </c>
-      <c r="R60" s="35"/>
-      <c r="S60" s="49"/>
+        <v>7.3325999999999993</v>
+      </c>
+      <c r="R60" s="73"/>
+      <c r="S60" s="64"/>
     </row>
     <row r="61" spans="1:19" s="1" customFormat="1">
       <c r="A61" s="32"/>
@@ -9090,50 +9270,52 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="38" t="s">
-        <v>299</v>
+      <c r="C61" s="34" t="s">
+        <v>294</v>
       </c>
       <c r="D61" s="37" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="E61" s="37" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="H61" s="37" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="I61" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J61" s="37" t="s">
-        <v>328</v>
-      </c>
-      <c r="K61" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="K61" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="L61" s="37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M61" s="35">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="N61" s="37">
-        <v>31</v>
-      </c>
-      <c r="O61" s="46" t="s">
-        <v>34</v>
+        <v>11</v>
+      </c>
+      <c r="O61" s="43" t="s">
+        <v>365</v>
       </c>
       <c r="P61" s="44">
-        <v>0.59030000000000005</v>
+        <v>6.25</v>
       </c>
       <c r="Q61" s="44">
         <f t="shared" si="5"/>
-        <v>18.299300000000002</v>
+        <v>68.75</v>
       </c>
       <c r="R61" s="37"/>
       <c r="S61" s="37"/>
@@ -9145,30 +9327,32 @@
         <v>53</v>
       </c>
       <c r="C62" s="34" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D62" s="35" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="E62" s="35" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="F62" s="35" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="G62" s="35" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="I62" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J62" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="K62" s="35"/>
+        <v>317</v>
+      </c>
+      <c r="K62" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="L62" s="35">
         <v>1</v>
       </c>
@@ -9183,11 +9367,11 @@
         <v>34</v>
       </c>
       <c r="P62" s="42">
-        <v>0.36120000000000002</v>
+        <v>0.26750000000000002</v>
       </c>
       <c r="Q62" s="42">
         <f t="shared" si="5"/>
-        <v>3.9732000000000003</v>
+        <v>2.9425000000000003</v>
       </c>
       <c r="R62" s="35"/>
       <c r="S62" s="49"/>
@@ -9199,140 +9383,138 @@
         <v>54</v>
       </c>
       <c r="C63" s="38" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D63" s="37" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="E63" s="37" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="H63" s="37" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="I63" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J63" s="37" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="K63" s="37"/>
       <c r="L63" s="37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M63" s="35">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="N63" s="37">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="O63" s="46" t="s">
         <v>34</v>
       </c>
       <c r="P63" s="44">
-        <v>0.16880000000000001</v>
+        <v>0.59030000000000005</v>
       </c>
       <c r="Q63" s="44">
         <f t="shared" si="5"/>
-        <v>2.532</v>
+        <v>18.299300000000002</v>
       </c>
       <c r="R63" s="37"/>
       <c r="S63" s="37"/>
     </row>
-    <row r="64" spans="1:19" s="76" customFormat="1">
-      <c r="A64" s="69"/>
-      <c r="B64" s="77">
+    <row r="64" spans="1:19" s="1" customFormat="1">
+      <c r="A64" s="32"/>
+      <c r="B64" s="33">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="71" t="s">
-        <v>299</v>
-      </c>
-      <c r="D64" s="73" t="s">
-        <v>341</v>
-      </c>
-      <c r="E64" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="F64" s="73" t="s">
-        <v>343</v>
-      </c>
-      <c r="G64" s="73" t="s">
-        <v>344</v>
-      </c>
-      <c r="H64" s="73" t="s">
+      <c r="C64" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="D64" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="E64" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="F64" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="G64" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="I64" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="J64" s="73" t="s">
-        <v>345</v>
-      </c>
-      <c r="K64" s="73"/>
-      <c r="L64" s="73">
+      <c r="H64" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="I64" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J64" s="35" t="s">
+        <v>329</v>
+      </c>
+      <c r="K64" s="35"/>
+      <c r="L64" s="35">
         <v>1</v>
       </c>
-      <c r="M64" s="73">
+      <c r="M64" s="35">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N64" s="73">
+      <c r="N64" s="35">
         <v>11</v>
       </c>
-      <c r="O64" s="78" t="s">
-        <v>34</v>
-      </c>
-      <c r="P64" s="79">
-        <v>0.96409999999999996</v>
-      </c>
-      <c r="Q64" s="79">
+      <c r="O64" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="P64" s="42">
+        <v>0.36120000000000002</v>
+      </c>
+      <c r="Q64" s="42">
         <f t="shared" si="5"/>
-        <v>10.6051</v>
-      </c>
-      <c r="R64" s="73"/>
-      <c r="S64" s="64"/>
-    </row>
-    <row r="65" spans="1:19" s="1" customFormat="1" ht="36">
+        <v>3.9732000000000003</v>
+      </c>
+      <c r="R64" s="35"/>
+      <c r="S64" s="49"/>
+    </row>
+    <row r="65" spans="1:19" s="1" customFormat="1">
       <c r="A65" s="32"/>
       <c r="B65" s="36">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="C65" s="38" t="s">
-        <v>346</v>
+        <v>294</v>
       </c>
       <c r="D65" s="37" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="E65" s="37" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>173</v>
+        <v>332</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="I65" s="37" t="s">
         <v>31</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>351</v>
-      </c>
-      <c r="K65" s="37" t="s">
-        <v>352</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="K65" s="37"/>
       <c r="L65" s="37">
         <v>1</v>
       </c>
@@ -9341,17 +9523,17 @@
         <v>10</v>
       </c>
       <c r="N65" s="37">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O65" s="46" t="s">
         <v>34</v>
       </c>
       <c r="P65" s="44">
-        <v>6.6100000000000006E-2</v>
+        <v>0.16880000000000001</v>
       </c>
       <c r="Q65" s="44">
         <f t="shared" si="5"/>
-        <v>1.3220000000000001</v>
+        <v>2.532</v>
       </c>
       <c r="R65" s="37"/>
       <c r="S65" s="37"/>
@@ -9362,33 +9544,31 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="80" t="s">
-        <v>346</v>
+      <c r="C66" s="71" t="s">
+        <v>294</v>
       </c>
       <c r="D66" s="73" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="E66" s="73" t="s">
-        <v>354</v>
-      </c>
-      <c r="F66" s="72" t="s">
-        <v>173</v>
+        <v>337</v>
+      </c>
+      <c r="F66" s="73" t="s">
+        <v>338</v>
       </c>
       <c r="G66" s="73" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="H66" s="73" t="s">
-        <v>356</v>
+        <v>322</v>
       </c>
       <c r="I66" s="72" t="s">
         <v>31</v>
       </c>
       <c r="J66" s="73" t="s">
-        <v>357</v>
-      </c>
-      <c r="K66" s="73" t="s">
-        <v>358</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="K66" s="73"/>
       <c r="L66" s="73">
         <v>1</v>
       </c>
@@ -9397,125 +9577,131 @@
         <v>10</v>
       </c>
       <c r="N66" s="73">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O66" s="78" t="s">
         <v>34</v>
       </c>
       <c r="P66" s="79">
-        <v>0.1401</v>
+        <v>0.96409999999999996</v>
       </c>
       <c r="Q66" s="79">
         <f t="shared" si="5"/>
-        <v>2.1015000000000001</v>
+        <v>10.6051</v>
       </c>
       <c r="R66" s="73"/>
       <c r="S66" s="64"/>
     </row>
-    <row r="67" spans="1:19">
-      <c r="A67" s="2"/>
-      <c r="B67" s="33">
+    <row r="67" spans="1:19" s="1" customFormat="1" ht="36">
+      <c r="A67" s="32"/>
+      <c r="B67" s="36">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="C67" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D67" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="E67" s="35" t="s">
-        <v>365</v>
+        <v>341</v>
+      </c>
+      <c r="D67" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="E67" s="37" t="s">
+        <v>343</v>
       </c>
       <c r="F67" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G67" s="35" t="s">
-        <v>366</v>
-      </c>
-      <c r="H67" s="35" t="s">
-        <v>31</v>
+        <v>168</v>
+      </c>
+      <c r="G67" s="37" t="s">
+        <v>344</v>
+      </c>
+      <c r="H67" s="37" t="s">
+        <v>345</v>
       </c>
       <c r="I67" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J67" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="K67" s="35"/>
-      <c r="L67" s="35">
-        <v>5</v>
+      <c r="J67" s="37" t="s">
+        <v>346</v>
+      </c>
+      <c r="K67" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="L67" s="37">
+        <v>1</v>
       </c>
       <c r="M67" s="35">
         <f t="shared" si="4"/>
-        <v>50</v>
-      </c>
-      <c r="N67" s="35">
-        <v>51</v>
-      </c>
-      <c r="O67" s="41" t="s">
-        <v>371</v>
-      </c>
-      <c r="P67" s="42">
-        <v>7.5</v>
-      </c>
-      <c r="Q67" s="42">
+        <v>10</v>
+      </c>
+      <c r="N67" s="37">
+        <v>20</v>
+      </c>
+      <c r="O67" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="P67" s="44">
+        <v>6.6100000000000006E-2</v>
+      </c>
+      <c r="Q67" s="44">
         <f t="shared" si="5"/>
-        <v>382.5</v>
-      </c>
-      <c r="R67" s="35"/>
-      <c r="S67" s="64"/>
-    </row>
-    <row r="68" spans="1:19">
-      <c r="A68" s="2"/>
-      <c r="B68" s="33">
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="R67" s="37"/>
+      <c r="S67" s="37"/>
+    </row>
+    <row r="68" spans="1:19" s="76" customFormat="1">
+      <c r="A68" s="69"/>
+      <c r="B68" s="77">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D68" s="35"/>
-      <c r="E68" s="35" t="s">
-        <v>367</v>
-      </c>
-      <c r="F68" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G68" s="35" t="s">
-        <v>368</v>
-      </c>
-      <c r="H68" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="I68" s="37"/>
-      <c r="J68" s="35" t="s">
-        <v>369</v>
-      </c>
-      <c r="K68" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="L68" s="35">
+      <c r="C68" s="80" t="s">
+        <v>341</v>
+      </c>
+      <c r="D68" s="73" t="s">
+        <v>348</v>
+      </c>
+      <c r="E68" s="73" t="s">
+        <v>349</v>
+      </c>
+      <c r="F68" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="G68" s="73" t="s">
+        <v>350</v>
+      </c>
+      <c r="H68" s="73" t="s">
+        <v>351</v>
+      </c>
+      <c r="I68" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="J68" s="73" t="s">
+        <v>352</v>
+      </c>
+      <c r="K68" s="73" t="s">
+        <v>353</v>
+      </c>
+      <c r="L68" s="73">
         <v>1</v>
       </c>
-      <c r="M68" s="35">
+      <c r="M68" s="73">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N68" s="35">
-        <v>11</v>
-      </c>
-      <c r="O68" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="P68" s="42">
-        <v>0.2069</v>
-      </c>
-      <c r="Q68" s="42">
+      <c r="N68" s="73">
+        <v>15</v>
+      </c>
+      <c r="O68" s="78" t="s">
+        <v>34</v>
+      </c>
+      <c r="P68" s="79">
+        <v>0.1401</v>
+      </c>
+      <c r="Q68" s="79">
         <f t="shared" si="5"/>
-        <v>2.2759</v>
-      </c>
-      <c r="R68" s="35"/>
+        <v>2.1015000000000001</v>
+      </c>
+      <c r="R68" s="73"/>
       <c r="S68" s="64"/>
     </row>
     <row r="69" spans="1:19">
@@ -9525,95 +9711,205 @@
         <v>60</v>
       </c>
       <c r="C69" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="D69" s="35"/>
+        <v>359</v>
+      </c>
+      <c r="D69" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="E69" s="35" t="s">
-        <v>372</v>
-      </c>
-      <c r="F69" s="37"/>
+        <v>360</v>
+      </c>
+      <c r="F69" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="G69" s="35" t="s">
-        <v>370</v>
-      </c>
-      <c r="H69" s="35"/>
-      <c r="I69" s="37"/>
-      <c r="J69" s="35"/>
+        <v>361</v>
+      </c>
+      <c r="H69" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I69" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="35" t="s">
+        <v>31</v>
+      </c>
       <c r="K69" s="35"/>
       <c r="L69" s="35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M69" s="35">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N69" s="35">
-        <v>60</v>
-      </c>
-      <c r="O69" s="41"/>
-      <c r="P69" s="42"/>
-      <c r="Q69" s="42"/>
+        <v>51</v>
+      </c>
+      <c r="O69" s="41" t="s">
+        <v>363</v>
+      </c>
+      <c r="P69" s="42">
+        <v>7.5</v>
+      </c>
+      <c r="Q69" s="42">
+        <f t="shared" si="5"/>
+        <v>382.5</v>
+      </c>
       <c r="R69" s="35"/>
       <c r="S69" s="64"/>
     </row>
-    <row r="70" spans="1:19" ht="18.75">
+    <row r="70" spans="1:19">
       <c r="A70" s="2"/>
-      <c r="B70" s="51"/>
-      <c r="C70" s="52"/>
-      <c r="D70" s="53"/>
-      <c r="E70" s="54"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="56"/>
-      <c r="H70" s="55"/>
-      <c r="I70" s="56"/>
-      <c r="J70" s="55"/>
-      <c r="K70" s="56"/>
-      <c r="L70" s="56"/>
-      <c r="M70" s="56"/>
-      <c r="N70" s="85" t="s">
+      <c r="B70" s="33">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="C70" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="O70" s="86"/>
-      <c r="P70" s="86"/>
-      <c r="Q70" s="61">
-        <f>SUM(Q10:Q69)</f>
-        <v>735.56609999999989</v>
-      </c>
-      <c r="R70" s="89"/>
-      <c r="S70" s="90"/>
-    </row>
-    <row r="71" spans="1:19" ht="18.75">
+      <c r="D70" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="95" t="s">
+        <v>384</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70" s="95" t="s">
+        <v>383</v>
+      </c>
+      <c r="H70" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="93" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="95" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L70" s="35">
+        <v>1</v>
+      </c>
+      <c r="M70" s="35">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N70" s="35">
+        <v>11</v>
+      </c>
+      <c r="O70" s="41" t="s">
+        <v>385</v>
+      </c>
+      <c r="P70" s="42">
+        <v>1.32</v>
+      </c>
+      <c r="Q70" s="42">
+        <f t="shared" si="5"/>
+        <v>14.520000000000001</v>
+      </c>
+      <c r="R70" s="35"/>
+      <c r="S70" s="64"/>
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71" s="2"/>
-      <c r="B71" s="57"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="60"/>
-      <c r="G71" s="60"/>
-      <c r="H71" s="60"/>
-      <c r="I71" s="60"/>
-      <c r="J71" s="60"/>
-      <c r="K71" s="60"/>
-      <c r="L71" s="60"/>
-      <c r="M71" s="60"/>
-      <c r="N71" s="85" t="s">
-        <v>360</v>
-      </c>
-      <c r="O71" s="86"/>
-      <c r="P71" s="86"/>
-      <c r="Q71" s="62">
-        <f>Q70/10</f>
-        <v>73.556609999999992</v>
-      </c>
-      <c r="R71" s="91"/>
-      <c r="S71" s="92"/>
+      <c r="B71" s="33">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="C71" s="38" t="s">
+        <v>359</v>
+      </c>
+      <c r="D71" s="35"/>
+      <c r="E71" s="35" t="s">
+        <v>364</v>
+      </c>
+      <c r="F71" s="37"/>
+      <c r="G71" s="35" t="s">
+        <v>362</v>
+      </c>
+      <c r="H71" s="35"/>
+      <c r="I71" s="37"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
+      <c r="L71" s="35">
+        <v>6</v>
+      </c>
+      <c r="M71" s="35">
+        <f t="shared" si="4"/>
+        <v>60</v>
+      </c>
+      <c r="N71" s="35">
+        <v>60</v>
+      </c>
+      <c r="O71" s="41"/>
+      <c r="P71" s="42"/>
+      <c r="Q71" s="42"/>
+      <c r="R71" s="35"/>
+      <c r="S71" s="64"/>
+    </row>
+    <row r="72" spans="1:19" ht="18.75">
+      <c r="A72" s="2"/>
+      <c r="B72" s="51"/>
+      <c r="C72" s="52"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="54"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="56"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="56"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="56"/>
+      <c r="L72" s="56"/>
+      <c r="M72" s="56"/>
+      <c r="N72" s="85" t="s">
+        <v>354</v>
+      </c>
+      <c r="O72" s="86"/>
+      <c r="P72" s="86"/>
+      <c r="Q72" s="61">
+        <f>SUM(Q10:Q71)</f>
+        <v>747.97019999999998</v>
+      </c>
+      <c r="R72" s="89"/>
+      <c r="S72" s="90"/>
+    </row>
+    <row r="73" spans="1:19" ht="18.75">
+      <c r="A73" s="2"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
+      <c r="J73" s="60"/>
+      <c r="K73" s="60"/>
+      <c r="L73" s="60"/>
+      <c r="M73" s="60"/>
+      <c r="N73" s="85" t="s">
+        <v>355</v>
+      </c>
+      <c r="O73" s="86"/>
+      <c r="P73" s="86"/>
+      <c r="Q73" s="62">
+        <f>Q72/10</f>
+        <v>74.797020000000003</v>
+      </c>
+      <c r="R73" s="91"/>
+      <c r="S73" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="K1:S1"/>
-    <mergeCell ref="N70:P70"/>
-    <mergeCell ref="N71:P71"/>
+    <mergeCell ref="N72:P72"/>
+    <mergeCell ref="N73:P73"/>
     <mergeCell ref="S3:S8"/>
-    <mergeCell ref="R70:S71"/>
+    <mergeCell ref="R72:S73"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O10" r:id="rId1"/>
@@ -9632,48 +9928,50 @@
     <hyperlink ref="O23" r:id="rId14"/>
     <hyperlink ref="O24" r:id="rId15"/>
     <hyperlink ref="O25" r:id="rId16"/>
-    <hyperlink ref="O27" r:id="rId17"/>
-    <hyperlink ref="O28" r:id="rId18"/>
-    <hyperlink ref="O29" r:id="rId19"/>
-    <hyperlink ref="O30" r:id="rId20"/>
-    <hyperlink ref="O31" r:id="rId21"/>
-    <hyperlink ref="O32" r:id="rId22"/>
-    <hyperlink ref="O35" r:id="rId23"/>
-    <hyperlink ref="O36" r:id="rId24"/>
-    <hyperlink ref="O37" r:id="rId25"/>
-    <hyperlink ref="O38" r:id="rId26"/>
-    <hyperlink ref="O39" r:id="rId27"/>
-    <hyperlink ref="O40" r:id="rId28"/>
-    <hyperlink ref="O41" r:id="rId29"/>
-    <hyperlink ref="O42" r:id="rId30"/>
-    <hyperlink ref="O44" r:id="rId31"/>
-    <hyperlink ref="O45" r:id="rId32"/>
-    <hyperlink ref="O46" r:id="rId33"/>
-    <hyperlink ref="O47" r:id="rId34"/>
-    <hyperlink ref="O48" r:id="rId35"/>
-    <hyperlink ref="O49" r:id="rId36"/>
-    <hyperlink ref="O50" r:id="rId37"/>
-    <hyperlink ref="O51" r:id="rId38"/>
-    <hyperlink ref="O52" r:id="rId39"/>
-    <hyperlink ref="O53" r:id="rId40"/>
-    <hyperlink ref="O54" r:id="rId41"/>
-    <hyperlink ref="O55" r:id="rId42"/>
-    <hyperlink ref="O56" r:id="rId43"/>
-    <hyperlink ref="O58" r:id="rId44"/>
-    <hyperlink ref="O60" r:id="rId45"/>
-    <hyperlink ref="O61" r:id="rId46"/>
-    <hyperlink ref="O62" r:id="rId47"/>
-    <hyperlink ref="O63" r:id="rId48"/>
-    <hyperlink ref="O64" r:id="rId49"/>
-    <hyperlink ref="O65" r:id="rId50"/>
-    <hyperlink ref="O66" r:id="rId51"/>
-    <hyperlink ref="O26" r:id="rId52"/>
-    <hyperlink ref="O68" r:id="rId53"/>
-    <hyperlink ref="O67" r:id="rId54"/>
-    <hyperlink ref="O59" r:id="rId55"/>
-    <hyperlink ref="O57" r:id="rId56"/>
+    <hyperlink ref="O28" r:id="rId17"/>
+    <hyperlink ref="O29" r:id="rId18"/>
+    <hyperlink ref="O30" r:id="rId19"/>
+    <hyperlink ref="O32" r:id="rId20"/>
+    <hyperlink ref="O33" r:id="rId21"/>
+    <hyperlink ref="O36" r:id="rId22"/>
+    <hyperlink ref="O37" r:id="rId23"/>
+    <hyperlink ref="O38" r:id="rId24"/>
+    <hyperlink ref="O39" r:id="rId25"/>
+    <hyperlink ref="O40" r:id="rId26"/>
+    <hyperlink ref="O41" r:id="rId27"/>
+    <hyperlink ref="O42" r:id="rId28"/>
+    <hyperlink ref="O43" r:id="rId29"/>
+    <hyperlink ref="O45" r:id="rId30"/>
+    <hyperlink ref="O46" r:id="rId31"/>
+    <hyperlink ref="O47" r:id="rId32"/>
+    <hyperlink ref="O48" r:id="rId33"/>
+    <hyperlink ref="O49" r:id="rId34"/>
+    <hyperlink ref="O50" r:id="rId35"/>
+    <hyperlink ref="O51" r:id="rId36"/>
+    <hyperlink ref="O52" r:id="rId37"/>
+    <hyperlink ref="O53" r:id="rId38"/>
+    <hyperlink ref="O54" r:id="rId39"/>
+    <hyperlink ref="O55" r:id="rId40"/>
+    <hyperlink ref="O56" r:id="rId41"/>
+    <hyperlink ref="O58" r:id="rId42"/>
+    <hyperlink ref="O60" r:id="rId43"/>
+    <hyperlink ref="O62" r:id="rId44"/>
+    <hyperlink ref="O63" r:id="rId45"/>
+    <hyperlink ref="O64" r:id="rId46"/>
+    <hyperlink ref="O65" r:id="rId47"/>
+    <hyperlink ref="O66" r:id="rId48"/>
+    <hyperlink ref="O67" r:id="rId49"/>
+    <hyperlink ref="O68" r:id="rId50"/>
+    <hyperlink ref="O26" r:id="rId51"/>
+    <hyperlink ref="O69" r:id="rId52"/>
+    <hyperlink ref="O61" r:id="rId53"/>
+    <hyperlink ref="O59" r:id="rId54"/>
+    <hyperlink ref="O27" r:id="rId55"/>
+    <hyperlink ref="O31" r:id="rId56"/>
+    <hyperlink ref="O57" r:id="rId57"/>
+    <hyperlink ref="O70" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId57"/>
+  <drawing r:id="rId59"/>
 </worksheet>
 </file>
--- a/Design Files/DC-Motor-Driver/Deliverables/BOM/eSpark BOM.xlsx
+++ b/Design Files/DC-Motor-Driver/Deliverables/BOM/eSpark BOM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="390">
   <si>
     <t>Component list</t>
   </si>
@@ -1178,6 +1178,18 @@
   </si>
   <si>
     <t>Aliexpress</t>
+  </si>
+  <si>
+    <t>Battery base CR2032 SMD Battery Connectors ROHS</t>
+  </si>
+  <si>
+    <t>CR2032-BS-6-1</t>
+  </si>
+  <si>
+    <t>Q&amp;J</t>
+  </si>
+  <si>
+    <t>C70377</t>
   </si>
 </sst>
 </file>
@@ -1877,6 +1889,15 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1907,15 +1928,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2301,7 +2313,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="63" customWidth="1"/>
@@ -2326,7 +2338,7 @@
     <col min="22" max="22" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:26">
       <c r="A1" s="2"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2337,17 +2349,17 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
-    </row>
-    <row r="2" spans="1:22" ht="31.5">
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="87"/>
+    </row>
+    <row r="2" spans="1:26" ht="31.5">
       <c r="A2" s="2"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6"/>
@@ -2372,7 +2384,7 @@
       <c r="R2" s="9"/>
       <c r="S2" s="48"/>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:26">
       <c r="A3" s="2"/>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
@@ -2395,9 +2407,9 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
-      <c r="S3" s="87"/>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="S3" s="90"/>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="2"/>
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
@@ -2420,9 +2432,9 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
-      <c r="S4" s="88"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="S4" s="91"/>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="2"/>
       <c r="B5" s="10"/>
       <c r="C5" s="11"/>
@@ -2445,9 +2457,9 @@
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
-      <c r="S5" s="88"/>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="S5" s="91"/>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="2"/>
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
@@ -2466,9 +2478,9 @@
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
-      <c r="S6" s="88"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="S6" s="91"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="2"/>
       <c r="B7" s="22"/>
       <c r="C7" s="23"/>
@@ -2487,9 +2499,9 @@
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
-      <c r="S7" s="88"/>
-    </row>
-    <row r="8" spans="1:22" ht="15.75" thickBot="1">
+      <c r="S7" s="91"/>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" thickBot="1">
       <c r="A8" s="2"/>
       <c r="B8" s="27"/>
       <c r="C8" s="28"/>
@@ -2508,9 +2520,9 @@
       <c r="P8" s="26"/>
       <c r="Q8" s="26"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="88"/>
-    </row>
-    <row r="9" spans="1:22" ht="15.75" thickBot="1">
+      <c r="S8" s="91"/>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" thickBot="1">
       <c r="A9" s="2"/>
       <c r="B9" s="31" t="s">
         <v>7</v>
@@ -2567,7 +2579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:26">
       <c r="A10" s="2"/>
       <c r="B10" s="33">
         <f t="shared" ref="B10:B71" si="0">ROW(B10)-ROW($B$9)</f>
@@ -2623,7 +2635,7 @@
       <c r="R10" s="35"/>
       <c r="S10" s="64"/>
     </row>
-    <row r="11" spans="1:22" s="1" customFormat="1" ht="36">
+    <row r="11" spans="1:26" s="1" customFormat="1" ht="36">
       <c r="A11" s="32"/>
       <c r="B11" s="36">
         <f t="shared" si="0"/>
@@ -2680,8 +2692,12 @@
       <c r="S11" s="37"/>
       <c r="U11"/>
       <c r="V11"/>
-    </row>
-    <row r="12" spans="1:22" ht="24">
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+    </row>
+    <row r="12" spans="1:26" ht="24">
       <c r="A12" s="2"/>
       <c r="B12" s="33">
         <f t="shared" si="0"/>
@@ -2737,7 +2753,7 @@
       <c r="R12" s="35"/>
       <c r="S12" s="64"/>
     </row>
-    <row r="13" spans="1:22" ht="24">
+    <row r="13" spans="1:26" ht="24">
       <c r="A13" s="2"/>
       <c r="B13" s="36">
         <f t="shared" si="0"/>
@@ -2793,7 +2809,7 @@
       <c r="R13" s="37"/>
       <c r="S13" s="37"/>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:26">
       <c r="A14" s="2"/>
       <c r="B14" s="33">
         <f t="shared" si="0"/>
@@ -2849,7 +2865,7 @@
       <c r="R14" s="35"/>
       <c r="S14" s="64"/>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:26">
       <c r="A15" s="2"/>
       <c r="B15" s="36">
         <f t="shared" si="0"/>
@@ -2905,7 +2921,7 @@
       <c r="R15" s="37"/>
       <c r="S15" s="37"/>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:26">
       <c r="A16" s="2"/>
       <c r="B16" s="33">
         <f t="shared" si="0"/>
@@ -3530,25 +3546,25 @@
       <c r="C27" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="93" t="s">
+      <c r="D27" s="83" t="s">
         <v>366</v>
       </c>
-      <c r="E27" s="93" t="s">
+      <c r="E27" s="83" t="s">
         <v>367</v>
       </c>
-      <c r="F27" s="93" t="s">
+      <c r="F27" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="G27" s="93" t="s">
+      <c r="G27" s="83" t="s">
         <v>368</v>
       </c>
-      <c r="H27" s="93" t="s">
+      <c r="H27" s="83" t="s">
         <v>369</v>
       </c>
       <c r="I27" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="93" t="s">
+      <c r="J27" s="83" t="s">
         <v>370</v>
       </c>
       <c r="K27" s="37" t="s">
@@ -3751,34 +3767,34 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="94" t="s">
+      <c r="C31" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="E31" s="93" t="s">
+      <c r="E31" s="83" t="s">
         <v>372</v>
       </c>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="83" t="s">
         <v>373</v>
       </c>
-      <c r="G31" s="93" t="s">
+      <c r="G31" s="83" t="s">
         <v>374</v>
       </c>
-      <c r="H31" s="93" t="s">
+      <c r="H31" s="83" t="s">
         <v>375</v>
       </c>
-      <c r="I31" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="93" t="s">
+      <c r="I31" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="83" t="s">
         <v>376</v>
       </c>
-      <c r="K31" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="93">
+      <c r="K31" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="83">
         <v>1</v>
       </c>
       <c r="M31" s="35">
@@ -4095,28 +4111,28 @@
       <c r="D37" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="E37" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" s="37" t="s">
+      <c r="E37" s="83" t="s">
+        <v>386</v>
+      </c>
+      <c r="F37" s="83" t="s">
         <v>168</v>
       </c>
-      <c r="G37" s="35" t="s">
-        <v>175</v>
-      </c>
-      <c r="H37" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="K37" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="L37" s="35">
+      <c r="G37" s="83" t="s">
+        <v>387</v>
+      </c>
+      <c r="H37" s="83" t="s">
+        <v>388</v>
+      </c>
+      <c r="I37" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="83" t="s">
+        <v>389</v>
+      </c>
+      <c r="K37" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="L37" s="83">
         <v>1</v>
       </c>
       <c r="M37" s="35">
@@ -4130,11 +4146,11 @@
         <v>34</v>
       </c>
       <c r="P37" s="42">
-        <v>0.13009999999999999</v>
+        <v>0.15590000000000001</v>
       </c>
       <c r="Q37" s="42">
         <f t="shared" si="2"/>
-        <v>1.3009999999999999</v>
+        <v>1.5590000000000002</v>
       </c>
       <c r="R37" s="35"/>
       <c r="S37" s="64"/>
@@ -4754,7 +4770,7 @@
       <c r="R48" s="37"/>
       <c r="S48" s="37"/>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:26">
       <c r="A49" s="2"/>
       <c r="B49" s="33">
         <f t="shared" si="0"/>
@@ -4810,7 +4826,7 @@
       <c r="R49" s="35"/>
       <c r="S49" s="64"/>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:26">
       <c r="A50" s="2"/>
       <c r="B50" s="36">
         <f t="shared" si="0"/>
@@ -4866,7 +4882,7 @@
       <c r="R50" s="37"/>
       <c r="S50" s="37"/>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:26">
       <c r="A51" s="2"/>
       <c r="B51" s="33">
         <f t="shared" si="0"/>
@@ -4922,7 +4938,7 @@
       <c r="R51" s="35"/>
       <c r="S51" s="64"/>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:26">
       <c r="A52" s="2"/>
       <c r="B52" s="36">
         <f t="shared" si="0"/>
@@ -4978,7 +4994,7 @@
       <c r="R52" s="37"/>
       <c r="S52" s="37"/>
     </row>
-    <row r="53" spans="1:22" ht="36">
+    <row r="53" spans="1:26" ht="36">
       <c r="A53" s="2"/>
       <c r="B53" s="33">
         <f t="shared" si="0"/>
@@ -5034,7 +5050,7 @@
       <c r="R53" s="35"/>
       <c r="S53" s="64"/>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:26">
       <c r="A54" s="2"/>
       <c r="B54" s="36">
         <f t="shared" si="0"/>
@@ -5090,7 +5106,7 @@
       <c r="R54" s="37"/>
       <c r="S54" s="37"/>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:26">
       <c r="A55" s="2"/>
       <c r="B55" s="33">
         <f t="shared" si="0"/>
@@ -5146,7 +5162,7 @@
       <c r="R55" s="35"/>
       <c r="S55" s="64"/>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:26">
       <c r="A56" s="2"/>
       <c r="B56" s="36">
         <f t="shared" si="0"/>
@@ -5202,37 +5218,37 @@
       <c r="R56" s="37"/>
       <c r="S56" s="37"/>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:26">
       <c r="A57" s="2"/>
       <c r="B57" s="36">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="94" t="s">
+      <c r="C57" s="84" t="s">
         <v>232</v>
       </c>
-      <c r="D57" s="93" t="s">
+      <c r="D57" s="83" t="s">
         <v>377</v>
       </c>
-      <c r="E57" s="93" t="s">
+      <c r="E57" s="83" t="s">
         <v>378</v>
       </c>
-      <c r="F57" s="93" t="s">
+      <c r="F57" s="83" t="s">
         <v>241</v>
       </c>
       <c r="G57" s="39" t="s">
         <v>379</v>
       </c>
-      <c r="H57" s="93" t="s">
+      <c r="H57" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="I57" s="93" t="s">
+      <c r="I57" s="83" t="s">
         <v>381</v>
       </c>
-      <c r="J57" s="93" t="s">
+      <c r="J57" s="83" t="s">
         <v>382</v>
       </c>
-      <c r="K57" s="93" t="s">
+      <c r="K57" s="83" t="s">
         <v>380</v>
       </c>
       <c r="L57" s="35">
@@ -5258,7 +5274,7 @@
       <c r="R57" s="35"/>
       <c r="S57" s="35"/>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:26">
       <c r="A58" s="2"/>
       <c r="B58" s="33">
         <f t="shared" si="0"/>
@@ -5314,7 +5330,7 @@
       <c r="R58" s="35"/>
       <c r="S58" s="64"/>
     </row>
-    <row r="59" spans="1:22" s="1" customFormat="1">
+    <row r="59" spans="1:26" s="1" customFormat="1">
       <c r="A59" s="32"/>
       <c r="B59" s="36">
         <f t="shared" si="0"/>
@@ -5371,8 +5387,12 @@
       <c r="S59" s="37"/>
       <c r="U59"/>
       <c r="V59"/>
-    </row>
-    <row r="60" spans="1:22">
+      <c r="W59"/>
+      <c r="X59"/>
+      <c r="Y59"/>
+      <c r="Z59"/>
+    </row>
+    <row r="60" spans="1:26">
       <c r="A60" s="2"/>
       <c r="B60" s="33">
         <f t="shared" si="0"/>
@@ -5428,7 +5448,7 @@
       <c r="R60" s="35"/>
       <c r="S60" s="64"/>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:26">
       <c r="A61" s="2"/>
       <c r="B61" s="36">
         <f t="shared" si="0"/>
@@ -5484,7 +5504,7 @@
       <c r="R61" s="37"/>
       <c r="S61" s="37"/>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:26">
       <c r="A62" s="2"/>
       <c r="B62" s="33">
         <f t="shared" si="0"/>
@@ -5540,7 +5560,7 @@
       <c r="R62" s="35"/>
       <c r="S62" s="64"/>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:26">
       <c r="A63" s="2"/>
       <c r="B63" s="36">
         <f t="shared" si="0"/>
@@ -5594,7 +5614,7 @@
       <c r="R63" s="37"/>
       <c r="S63" s="37"/>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:26">
       <c r="A64" s="2"/>
       <c r="B64" s="33">
         <f t="shared" si="0"/>
@@ -5910,7 +5930,7 @@
         <v>26</v>
       </c>
       <c r="O69" s="41" t="s">
-        <v>34</v>
+        <v>363</v>
       </c>
       <c r="P69" s="42">
         <v>7.5</v>
@@ -5931,25 +5951,25 @@
       <c r="C70" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="D70" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="E70" s="95" t="s">
+      <c r="D70" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="85" t="s">
         <v>384</v>
       </c>
       <c r="F70" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="G70" s="95" t="s">
+      <c r="G70" s="85" t="s">
         <v>383</v>
       </c>
       <c r="H70" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I70" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="J70" s="95" t="s">
+      <c r="I70" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="85" t="s">
         <v>31</v>
       </c>
       <c r="K70" s="35" t="s">
@@ -6029,17 +6049,17 @@
       <c r="K72" s="56"/>
       <c r="L72" s="56"/>
       <c r="M72" s="56"/>
-      <c r="N72" s="85" t="s">
+      <c r="N72" s="88" t="s">
         <v>354</v>
       </c>
-      <c r="O72" s="86"/>
-      <c r="P72" s="86"/>
+      <c r="O72" s="89"/>
+      <c r="P72" s="89"/>
       <c r="Q72" s="61">
         <f>SUM(Q10:Q71)</f>
-        <v>404.92770000000002</v>
-      </c>
-      <c r="R72" s="89"/>
-      <c r="S72" s="90"/>
+        <v>405.18570000000005</v>
+      </c>
+      <c r="R72" s="92"/>
+      <c r="S72" s="93"/>
     </row>
     <row r="73" spans="1:19" ht="18.75">
       <c r="A73" s="2"/>
@@ -6055,17 +6075,17 @@
       <c r="K73" s="60"/>
       <c r="L73" s="60"/>
       <c r="M73" s="60"/>
-      <c r="N73" s="85" t="s">
+      <c r="N73" s="88" t="s">
         <v>355</v>
       </c>
-      <c r="O73" s="86"/>
-      <c r="P73" s="86"/>
+      <c r="O73" s="89"/>
+      <c r="P73" s="89"/>
       <c r="Q73" s="62">
         <f>Q72/5</f>
-        <v>80.98554</v>
-      </c>
-      <c r="R73" s="91"/>
-      <c r="S73" s="92"/>
+        <v>81.037140000000008</v>
+      </c>
+      <c r="R73" s="94"/>
+      <c r="S73" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6098,42 +6118,42 @@
     <hyperlink ref="O32" r:id="rId20"/>
     <hyperlink ref="O33" r:id="rId21"/>
     <hyperlink ref="O36" r:id="rId22"/>
-    <hyperlink ref="O37" r:id="rId23"/>
-    <hyperlink ref="O38" r:id="rId24"/>
-    <hyperlink ref="O39" r:id="rId25"/>
-    <hyperlink ref="O40" r:id="rId26"/>
-    <hyperlink ref="O41" r:id="rId27"/>
-    <hyperlink ref="O42" r:id="rId28"/>
-    <hyperlink ref="O43" r:id="rId29"/>
-    <hyperlink ref="O45" r:id="rId30"/>
-    <hyperlink ref="O46" r:id="rId31"/>
-    <hyperlink ref="O47" r:id="rId32"/>
-    <hyperlink ref="O48" r:id="rId33"/>
-    <hyperlink ref="O49" r:id="rId34"/>
-    <hyperlink ref="O50" r:id="rId35"/>
-    <hyperlink ref="O51" r:id="rId36"/>
-    <hyperlink ref="O52" r:id="rId37"/>
-    <hyperlink ref="O53" r:id="rId38"/>
-    <hyperlink ref="O54" r:id="rId39"/>
-    <hyperlink ref="O55" r:id="rId40"/>
-    <hyperlink ref="O56" r:id="rId41"/>
-    <hyperlink ref="O58" r:id="rId42"/>
-    <hyperlink ref="O60" r:id="rId43"/>
-    <hyperlink ref="O62" r:id="rId44"/>
-    <hyperlink ref="O63" r:id="rId45"/>
-    <hyperlink ref="O64" r:id="rId46"/>
-    <hyperlink ref="O65" r:id="rId47"/>
-    <hyperlink ref="O66" r:id="rId48"/>
-    <hyperlink ref="O67" r:id="rId49"/>
-    <hyperlink ref="O68" r:id="rId50"/>
-    <hyperlink ref="O26" r:id="rId51"/>
-    <hyperlink ref="O69" r:id="rId52"/>
-    <hyperlink ref="O61" r:id="rId53"/>
-    <hyperlink ref="O59" r:id="rId54"/>
-    <hyperlink ref="O27" r:id="rId55"/>
-    <hyperlink ref="O31" r:id="rId56"/>
-    <hyperlink ref="O57" r:id="rId57"/>
-    <hyperlink ref="O70" r:id="rId58"/>
+    <hyperlink ref="O38" r:id="rId23"/>
+    <hyperlink ref="O39" r:id="rId24"/>
+    <hyperlink ref="O40" r:id="rId25"/>
+    <hyperlink ref="O41" r:id="rId26"/>
+    <hyperlink ref="O42" r:id="rId27"/>
+    <hyperlink ref="O43" r:id="rId28"/>
+    <hyperlink ref="O45" r:id="rId29"/>
+    <hyperlink ref="O46" r:id="rId30"/>
+    <hyperlink ref="O47" r:id="rId31"/>
+    <hyperlink ref="O48" r:id="rId32"/>
+    <hyperlink ref="O49" r:id="rId33"/>
+    <hyperlink ref="O50" r:id="rId34"/>
+    <hyperlink ref="O51" r:id="rId35"/>
+    <hyperlink ref="O52" r:id="rId36"/>
+    <hyperlink ref="O53" r:id="rId37"/>
+    <hyperlink ref="O54" r:id="rId38"/>
+    <hyperlink ref="O55" r:id="rId39"/>
+    <hyperlink ref="O56" r:id="rId40"/>
+    <hyperlink ref="O58" r:id="rId41"/>
+    <hyperlink ref="O60" r:id="rId42"/>
+    <hyperlink ref="O62" r:id="rId43"/>
+    <hyperlink ref="O63" r:id="rId44"/>
+    <hyperlink ref="O64" r:id="rId45"/>
+    <hyperlink ref="O65" r:id="rId46"/>
+    <hyperlink ref="O66" r:id="rId47"/>
+    <hyperlink ref="O67" r:id="rId48"/>
+    <hyperlink ref="O68" r:id="rId49"/>
+    <hyperlink ref="O26" r:id="rId50"/>
+    <hyperlink ref="O61" r:id="rId51"/>
+    <hyperlink ref="O59" r:id="rId52"/>
+    <hyperlink ref="O27" r:id="rId53"/>
+    <hyperlink ref="O31" r:id="rId54"/>
+    <hyperlink ref="O57" r:id="rId55"/>
+    <hyperlink ref="O70" r:id="rId56"/>
+    <hyperlink ref="O37" r:id="rId57"/>
+    <hyperlink ref="O69" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -6177,15 +6197,15 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
       <c r="J1" s="4"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="84"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="87"/>
     </row>
     <row r="2" spans="1:19" ht="31.5">
       <c r="A2" s="2"/>
@@ -6235,7 +6255,7 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="13"/>
-      <c r="S3" s="87"/>
+      <c r="S3" s="90"/>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2"/>
@@ -6260,7 +6280,7 @@
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
-      <c r="S4" s="88"/>
+      <c r="S4" s="91"/>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2"/>
@@ -6285,7 +6305,7 @@
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
-      <c r="S5" s="88"/>
+      <c r="S5" s="91"/>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="2"/>
@@ -6306,7 +6326,7 @@
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="17"/>
-      <c r="S6" s="88"/>
+      <c r="S6" s="91"/>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2"/>
@@ -6327,7 +6347,7 @@
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
       <c r="R7" s="26"/>
-      <c r="S7" s="88"/>
+      <c r="S7" s="91"/>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="2"/>
@@ -6348,7 +6368,7 @@
       <c r="P8" s="26"/>
       <c r="Q8" s="26"/>
       <c r="R8" s="26"/>
-      <c r="S8" s="88"/>
+      <c r="S8" s="91"/>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2"/>
@@ -7368,25 +7388,25 @@
       <c r="C27" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="93" t="s">
+      <c r="D27" s="83" t="s">
         <v>366</v>
       </c>
-      <c r="E27" s="93" t="s">
+      <c r="E27" s="83" t="s">
         <v>367</v>
       </c>
-      <c r="F27" s="93" t="s">
+      <c r="F27" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="G27" s="93" t="s">
+      <c r="G27" s="83" t="s">
         <v>368</v>
       </c>
-      <c r="H27" s="93" t="s">
+      <c r="H27" s="83" t="s">
         <v>369</v>
       </c>
       <c r="I27" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="J27" s="93" t="s">
+      <c r="J27" s="83" t="s">
         <v>370</v>
       </c>
       <c r="K27" s="37" t="s">
@@ -7589,34 +7609,34 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="94" t="s">
+      <c r="C31" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="E31" s="93" t="s">
+      <c r="E31" s="83" t="s">
         <v>372</v>
       </c>
-      <c r="F31" s="93" t="s">
+      <c r="F31" s="83" t="s">
         <v>373</v>
       </c>
-      <c r="G31" s="93" t="s">
+      <c r="G31" s="83" t="s">
         <v>374</v>
       </c>
-      <c r="H31" s="93" t="s">
+      <c r="H31" s="83" t="s">
         <v>375</v>
       </c>
-      <c r="I31" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="93" t="s">
+      <c r="I31" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="83" t="s">
         <v>376</v>
       </c>
-      <c r="K31" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="93">
+      <c r="K31" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="83">
         <v>1</v>
       </c>
       <c r="M31" s="73">
@@ -9046,31 +9066,31 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="94" t="s">
+      <c r="C57" s="84" t="s">
         <v>232</v>
       </c>
-      <c r="D57" s="93" t="s">
+      <c r="D57" s="83" t="s">
         <v>377</v>
       </c>
-      <c r="E57" s="93" t="s">
+      <c r="E57" s="83" t="s">
         <v>378</v>
       </c>
-      <c r="F57" s="93" t="s">
+      <c r="F57" s="83" t="s">
         <v>241</v>
       </c>
       <c r="G57" s="39" t="s">
         <v>379</v>
       </c>
-      <c r="H57" s="93" t="s">
+      <c r="H57" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="I57" s="93" t="s">
+      <c r="I57" s="83" t="s">
         <v>381</v>
       </c>
-      <c r="J57" s="93" t="s">
+      <c r="J57" s="83" t="s">
         <v>382</v>
       </c>
-      <c r="K57" s="93" t="s">
+      <c r="K57" s="83" t="s">
         <v>380</v>
       </c>
       <c r="L57" s="35">
@@ -9767,25 +9787,25 @@
       <c r="C70" s="38" t="s">
         <v>359</v>
       </c>
-      <c r="D70" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="E70" s="95" t="s">
+      <c r="D70" s="85" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="85" t="s">
         <v>384</v>
       </c>
       <c r="F70" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="G70" s="95" t="s">
+      <c r="G70" s="85" t="s">
         <v>383</v>
       </c>
       <c r="H70" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="I70" s="93" t="s">
-        <v>31</v>
-      </c>
-      <c r="J70" s="95" t="s">
+      <c r="I70" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="85" t="s">
         <v>31</v>
       </c>
       <c r="K70" s="35" t="s">
@@ -9865,17 +9885,17 @@
       <c r="K72" s="56"/>
       <c r="L72" s="56"/>
       <c r="M72" s="56"/>
-      <c r="N72" s="85" t="s">
+      <c r="N72" s="88" t="s">
         <v>354</v>
       </c>
-      <c r="O72" s="86"/>
-      <c r="P72" s="86"/>
+      <c r="O72" s="89"/>
+      <c r="P72" s="89"/>
       <c r="Q72" s="61">
         <f>SUM(Q10:Q71)</f>
         <v>747.97019999999998</v>
       </c>
-      <c r="R72" s="89"/>
-      <c r="S72" s="90"/>
+      <c r="R72" s="92"/>
+      <c r="S72" s="93"/>
     </row>
     <row r="73" spans="1:19" ht="18.75">
       <c r="A73" s="2"/>
@@ -9891,17 +9911,17 @@
       <c r="K73" s="60"/>
       <c r="L73" s="60"/>
       <c r="M73" s="60"/>
-      <c r="N73" s="85" t="s">
+      <c r="N73" s="88" t="s">
         <v>355</v>
       </c>
-      <c r="O73" s="86"/>
-      <c r="P73" s="86"/>
+      <c r="O73" s="89"/>
+      <c r="P73" s="89"/>
       <c r="Q73" s="62">
         <f>Q72/10</f>
         <v>74.797020000000003</v>
       </c>
-      <c r="R73" s="91"/>
-      <c r="S73" s="92"/>
+      <c r="R73" s="94"/>
+      <c r="S73" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="5">
